--- a/tracker-en.xlsx
+++ b/tracker-en.xlsx
@@ -1,36 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ce0e9fd63db271f8/HybrideFuelCo/Website/DataSheets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_0511C9F4F3D486ECA5EB7C25B8E3992DE872B485" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BD1B3468-ED64-4117-8A73-992E9B954CE5}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
-    <sheet name="Meal plan" sheetId="2" r:id="rId2"/>
-    <sheet name="Weight" sheetId="3" r:id="rId3"/>
-    <sheet name="Shopping" sheetId="4" r:id="rId4"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Meal plan" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Weight" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Shopping" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -39,289 +23,289 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="89">
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>HYBRIDFUELCO</t>
-  </si>
-  <si>
-    <t>PROGRESS TRACKER</t>
-  </si>
-  <si>
-    <t>Current weight</t>
-  </si>
-  <si>
-    <t>Last change</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Today</t>
-  </si>
-  <si>
-    <t>Weight trend</t>
-  </si>
-  <si>
-    <t>Today — meals</t>
-  </si>
-  <si>
-    <t>Mon</t>
-  </si>
-  <si>
-    <t>Breakfast</t>
-  </si>
-  <si>
-    <t>Lunch</t>
-  </si>
-  <si>
-    <t>Dinner</t>
-  </si>
-  <si>
-    <t>Snack</t>
-  </si>
-  <si>
-    <t>Day total</t>
-  </si>
-  <si>
-    <t>Daily macros — selected day</t>
-  </si>
-  <si>
-    <t>Protein</t>
-  </si>
-  <si>
-    <t>Carbs</t>
-  </si>
-  <si>
-    <t>Fat</t>
-  </si>
-  <si>
-    <t>MEAL PLAN</t>
-  </si>
-  <si>
-    <t>Replace this example week with your own plan from the app. The dashboard reads 'Today' from here.</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>Dish</t>
-  </si>
-  <si>
-    <t>Ingredients</t>
-  </si>
-  <si>
-    <t>kcal</t>
-  </si>
-  <si>
-    <t>Protein (g)</t>
-  </si>
-  <si>
-    <t>Carbs (g)</t>
-  </si>
-  <si>
-    <t>Fat (g)</t>
-  </si>
-  <si>
-    <t>key</t>
-  </si>
-  <si>
-    <t>Savoury oats with egg</t>
-  </si>
-  <si>
-    <t>60g oats, 2 eggs, 100g spinach</t>
-  </si>
-  <si>
-    <t>Chicken &amp; rice bowl</t>
-  </si>
-  <si>
-    <t>150g chicken, 70g rice, 150g veg</t>
-  </si>
-  <si>
-    <t>Lean mince pasta</t>
-  </si>
-  <si>
-    <t>130g mince, 70g pasta, tomato sauce</t>
-  </si>
-  <si>
-    <t>Quark with nuts</t>
-  </si>
-  <si>
-    <t>200g quark, 20g nuts</t>
-  </si>
-  <si>
-    <t>Tue</t>
-  </si>
-  <si>
-    <t>Quark with oats &amp; berries</t>
-  </si>
-  <si>
-    <t>250g quark, 40g oats, 100g berries</t>
-  </si>
-  <si>
-    <t>Tuna wrap</t>
-  </si>
-  <si>
-    <t>1 wrap, 100g tuna, 50g corn</t>
-  </si>
-  <si>
-    <t>Salmon with quinoa</t>
-  </si>
-  <si>
-    <t>125g salmon, 60g quinoa, 100g broccoli</t>
-  </si>
-  <si>
-    <t>Protein bar &amp; fruit</t>
-  </si>
-  <si>
-    <t>1 bar, 1 apple</t>
-  </si>
-  <si>
-    <t>Wed</t>
-  </si>
-  <si>
-    <t>High-protein pancakes</t>
-  </si>
-  <si>
-    <t>50g oat flour, 30g whey, 1 egg</t>
-  </si>
-  <si>
-    <t>Beef &amp; avocado bowl</t>
-  </si>
-  <si>
-    <t>150g lean beef, 80g avocado, 80g greens</t>
-  </si>
-  <si>
-    <t>Chicken &amp; sweet potato</t>
-  </si>
-  <si>
-    <t>160g chicken, 200g sweet potato, 150g veg</t>
-  </si>
-  <si>
-    <t>Skyr with honey</t>
-  </si>
-  <si>
-    <t>200g skyr, 15g honey</t>
-  </si>
-  <si>
-    <t>Thu</t>
-  </si>
-  <si>
-    <t>Fri</t>
-  </si>
-  <si>
-    <t>Sat</t>
-  </si>
-  <si>
-    <t>Sun</t>
-  </si>
-  <si>
-    <t>WEIGHT &amp; PROGRESS</t>
-  </si>
-  <si>
-    <t>Weigh in once a week at a fixed time. Enter date + weight; the chart and dashboard update automatically.</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Weight (kg)</t>
-  </si>
-  <si>
-    <t>Change (kg)</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>SHOPPING LIST</t>
-  </si>
-  <si>
-    <t>Your weekly list, by category. Tick what you already have.</t>
-  </si>
-  <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Got it?</t>
-  </si>
-  <si>
-    <t>Produce</t>
-  </si>
-  <si>
-    <t>Spinach 500g</t>
-  </si>
-  <si>
-    <t>Broccoli 400g</t>
-  </si>
-  <si>
-    <t>Apples 7</t>
-  </si>
-  <si>
-    <t>Berries 300g</t>
-  </si>
-  <si>
-    <t>Chicken 1kg</t>
-  </si>
-  <si>
-    <t>Lean beef 500g</t>
-  </si>
-  <si>
-    <t>Salmon 400g</t>
-  </si>
-  <si>
-    <t>Dairy</t>
-  </si>
-  <si>
-    <t>Low-fat quark 1kg</t>
-  </si>
-  <si>
-    <t>Skyr 500g</t>
-  </si>
-  <si>
-    <t>Eggs 12</t>
-  </si>
-  <si>
-    <t>Grains</t>
-  </si>
-  <si>
-    <t>Oats 500g</t>
-  </si>
-  <si>
-    <t>Rice 500g</t>
-  </si>
-  <si>
-    <t>Pasta 500g</t>
-  </si>
-  <si>
-    <t>✓</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="88">
+  <si>
+    <t xml:space="preserve">H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYBRIDFUELCO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROGRESS TRACKER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Current weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight trend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today — meals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lunch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daily macros — selected day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEAL PLAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Replace this example week with your own plan from the app. The dashboard reads 'Today' from here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ingredients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kcal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbs (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fat (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savoury oats with egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60g oats, 2 eggs, 100g spinach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicken &amp; rice bowl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150g chicken, 70g rice, 150g veg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lean mince pasta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">130g mince, 70g pasta, tomato sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quark with nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200g quark, 20g nuts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quark with oats &amp; berries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250g quark, 40g oats, 100g berries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuna wrap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 wrap, 100g tuna, 50g corn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmon with quinoa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125g salmon, 60g quinoa, 100g broccoli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein bar &amp; fruit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 bar, 1 apple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-protein pancakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50g oat flour, 30g whey, 1 egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beef &amp; avocado bowl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150g lean beef, 80g avocado, 80g greens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicken &amp; sweet potato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">160g chicken, 200g sweet potato, 150g veg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyr with honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200g skyr, 15g honey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WEIGHT &amp; PROGRESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weigh in once a week at a fixed time. Enter date + weight; the chart and dashboard update automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Change (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SHOPPING LIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your weekly list, by category. Tick what you already have.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Item</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Got it?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Produce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spinach 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoli 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apples 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berries 300g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicken 1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lean beef 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmon 400g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dairy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-fat quark 1kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skyr 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eggs 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grains</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oats 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rice 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pasta 500g</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="165" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="166" formatCode="#,##0&quot; kcal&quot;"/>
-    <numFmt numFmtId="167" formatCode="0&quot; g&quot;"/>
-    <numFmt numFmtId="168" formatCode="mm\-dd\-yyyy"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="\+0.0;\-0.0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="10">
+    <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
+    <numFmt numFmtId="166" formatCode="0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="167" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0&quot; kcal&quot;"/>
+    <numFmt numFmtId="169" formatCode="#,##0"/>
+    <numFmt numFmtId="170" formatCode="0&quot; g&quot;"/>
+    <numFmt numFmtId="171" formatCode="mm\-dd\-yyyy"/>
+    <numFmt numFmtId="172" formatCode="0.0"/>
+    <numFmt numFmtId="173" formatCode="\+0.0;\-0.0"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -330,138 +314,179 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="22"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="18"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF8C8C8C"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FF8C8C8C"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="24"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="24"/>
       <color rgb="FF1F9D55"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="16"/>
       <color rgb="FF1F9D55"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FFE8321E"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="12"/>
       <color rgb="FFE8321E"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="9"/>
       <color rgb="FFE8321E"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="13"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF444444"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="15"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i/>
+      <i val="true"/>
       <sz val="9"/>
       <color rgb="FF8C8C8C"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF8C8C8C"/>
       <name val="Arial"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -510,14 +535,14 @@
     </fill>
   </fills>
   <borders count="13">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFE8321E"/>
       </left>
@@ -530,7 +555,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FF1F9D55"/>
       </left>
@@ -543,7 +568,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFE8321E"/>
       </left>
@@ -556,7 +581,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FF1F9D55"/>
       </left>
@@ -569,7 +594,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFE8321E"/>
       </left>
@@ -582,7 +607,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thin">
         <color rgb="FFE6E6E6"/>
       </left>
@@ -597,7 +622,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top style="medium">
@@ -606,7 +631,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FF1F9D55"/>
       </left>
@@ -621,7 +646,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFFF6A52"/>
       </left>
@@ -634,7 +659,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFB9B9B9"/>
       </left>
@@ -647,7 +672,7 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFFF6A52"/>
       </left>
@@ -660,7 +685,7 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left style="thick">
         <color rgb="FFB9B9B9"/>
       </left>
@@ -674,115 +699,201 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="170" fontId="18" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="40">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="6" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -841,37 +952,18 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF444444"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="nl-NL"/>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -880,7 +972,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Weight!$B$3</c:f>
+              <c:f>Weight!B3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -890,9 +982,12 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="e8321e"/>
+            </a:solidFill>
             <a:ln w="28080">
               <a:solidFill>
-                <a:srgbClr val="E8321E"/>
+                <a:srgbClr val="e8321e"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -901,23 +996,15 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="nl-NL"/>
               </a:p>
             </c:txPr>
             <c:showLegendKey val="0"/>
@@ -925,9 +1012,8 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
-            <c:showLeaderLines val="0"/>
+            <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                 <c15:showLeaderLines val="1"/>
@@ -935,37 +1021,93 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:strRef>
               <c:f>Weight!$A$4:$A$30</c:f>
-              <c:numCache>
-                <c:formatCode>mm\-dd\-yyyy</c:formatCode>
+              <c:strCache>
                 <c:ptCount val="27"/>
                 <c:pt idx="0">
-                  <c:v>46271</c:v>
+                  <c:v>09-06-2026</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>46278</c:v>
+                  <c:v>09-13-2026</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>46285</c:v>
+                  <c:v>09-20-2026</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>46292</c:v>
+                  <c:v>09-27-2026</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>46299</c:v>
+                  <c:v>10-04-2026</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>46306</c:v>
+                  <c:v>10-11-2026</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>46313</c:v>
+                  <c:v>10-18-2026</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>46320</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>10-25-2026</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v/>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v/>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1001,20 +1143,7 @@
             </c:numRef>
           </c:val>
           <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-A7A7-4D84-9793-24304CD89A52}"/>
-            </c:ext>
-          </c:extLst>
         </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
         <c:hiLowLines>
           <c:spPr>
             <a:ln w="0">
@@ -1022,11 +1151,11 @@
             </a:ln>
           </c:spPr>
         </c:hiLowLines>
-        <c:smooth val="0"/>
+        <c:marker val="0"/>
         <c:axId val="63125726"/>
         <c:axId val="36317127"/>
       </c:lineChart>
-      <c:dateAx>
+      <c:catAx>
         <c:axId val="63125726"/>
         <c:scaling>
           <c:orientation val="minMax"/>
@@ -1050,22 +1179,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="nl-NL"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="36317127"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="days"/>
-      </c:dateAx>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:valAx>
         <c:axId val="36317127"/>
         <c:scaling>
@@ -1090,14 +1219,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1000" b="0" strike="noStrike" spc="-1">
+              <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
                 <a:solidFill>
                   <a:srgbClr val="000000"/>
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="nl-NL"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="63125726"/>
@@ -1113,29 +1241,23 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="FFFFFF"/>
+      <a:srgbClr val="ffffff"/>
     </a:solidFill>
     <a:ln w="9360">
       <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
+        <a:srgbClr val="d9d9d9"/>
       </a:solidFill>
       <a:round/>
     </a:ln>
   </c:spPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
@@ -1149,20 +1271,14 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>97920</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="0" name="Chart 1"/>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="0" y="1743120"/>
+        <a:ext cx="4139640" cy="1907640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1176,41 +1292,41 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -1218,12 +1334,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -1252,7 +1368,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1273,7 +1389,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1324,7 +1440,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1342,331 +1458,319 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFE8321E"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="12" width="9.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13" hidden="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="0" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+    <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="I1" s="12" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="I1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="N1">
-        <f>IFERROR(LOOKUP(2,1/(Weight!$B$4:$B$30&lt;&gt;""),Weight!$B$4:$B$30),"")</f>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="N1" s="4" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(Weight!$B$4:$B$30&lt;&gt;""),Weight!$B$4:$B$30),"")</f>
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-      <c r="N2">
-        <f>IFERROR(LOOKUP(2,1/(Weight!$C$4:$C$30&lt;&gt;""),Weight!$C$4:$C$30),"")</f>
-        <v>-0.20000000000000284</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="N3">
-        <f>IF(AND(N1&lt;&gt;"",N2&lt;&gt;""),N2/N1,"")</f>
-        <v>-2.2988505747126762E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="N2" s="4" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(Weight!$C$4:$C$30&lt;&gt;""),Weight!$C$4:$C$30),"")</f>
+        <v>-0.200000000000003</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="N3" s="0" t="n">
+        <f aca="false">IF(AND(N1&lt;&gt;"",N2&lt;&gt;""),N2/N1,"")</f>
+        <v>-0.00229885057471268</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="10" t="s">
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10" t="s">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="11" t="s">
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-    </row>
-    <row r="5" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9">
-        <f>N1</f>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="n">
+        <f aca="false">N1</f>
         <v>87</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="8">
-        <f>N2</f>
-        <v>-0.20000000000000284</v>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="8" t="n">
+        <f aca="false">N2</f>
+        <v>-0.200000000000003</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="7" t="str">
-        <f>IF(N3="","",IF(N3&lt;-0.01,"! Too fast",IF(N3&lt;-0.003,"✓ On track",IF(N3&lt;=0.003,"– Stable",IF(N3&lt;=0.01,"✓ On track","! Too fast")))))</f>
+      <c r="G5" s="9" t="str">
+        <f aca="false">IF(N3="","",IF(N3&lt;-0.01,"! Too fast",IF(N3&lt;-0.003,"✓ On track",IF(N3&lt;=0.003,"– Stable",IF(N3&lt;=0.01,"✓ On track","! Too fast")))))</f>
         <v>– Stable</v>
       </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="6">
-        <f>SUMIFS('Meal plan'!$E$4:$E$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
-        <v>1940</v>
-      </c>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="10" t="n">
+        <f aca="false">SUMIFS('Meal plan'!$E$4:$E$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
+        <v>2220</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="6"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="G6" s="9"/>
+      <c r="H6" s="9"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+    </row>
+    <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="4" t="s">
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G9" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="16" t="s">
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="13"/>
+    </row>
+    <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G9" s="14"/>
+      <c r="H9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="I9" s="2" t="str">
-        <f>IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Breakfast",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>High-protein pancakes</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="17">
-        <f>IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Breakfast",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>480</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G10" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="H10" s="16" t="s">
+      <c r="I9" s="16" t="str">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Breakfast",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>Savoury oats with egg</v>
+      </c>
+      <c r="J9" s="16"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="17" t="n">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Breakfast",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>640</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G10" s="14"/>
+      <c r="H10" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="2" t="str">
-        <f>IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Lunch",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>Beef &amp; avocado bowl</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="17">
-        <f>IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Lunch",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G11" s="15"/>
-      <c r="H11" s="16" t="s">
+      <c r="I10" s="16" t="str">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Lunch",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>Chicken &amp; rice bowl</v>
+      </c>
+      <c r="J10" s="16"/>
+      <c r="K10" s="16"/>
+      <c r="L10" s="17" t="n">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Lunch",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>560</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G11" s="14"/>
+      <c r="H11" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="I11" s="2" t="str">
-        <f>IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Dinner",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>Chicken &amp; sweet potato</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="17">
-        <f>IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Dinner",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>620</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G12" s="15"/>
-      <c r="H12" s="16" t="s">
+      <c r="I11" s="16" t="str">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Dinner",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>Lean mince pasta</v>
+      </c>
+      <c r="J11" s="16"/>
+      <c r="K11" s="16"/>
+      <c r="L11" s="17" t="n">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Dinner",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>720</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G12" s="14"/>
+      <c r="H12" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="I12" s="2" t="str">
-        <f>IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Snack",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>Skyr with honey</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="17">
-        <f>IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Snack",'Meal plan'!$I$4:$I$31,0)),"")</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G13" s="1" t="s">
+      <c r="I12" s="16" t="str">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$C$4:$C$31,MATCH($K$8&amp;"|"&amp;"Snack",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>Quark with nuts</v>
+      </c>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="17" t="n">
+        <f aca="false">IFERROR(INDEX('Meal plan'!$E$4:$E$31,MATCH($K$8&amp;"|"&amp;"Snack",'Meal plan'!$I$4:$I$31,0)),"")</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="G13" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="30">
-        <f>SUMIFS('Meal plan'!$E$4:$E$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
-        <v>1940</v>
-      </c>
-      <c r="K13" s="30"/>
-      <c r="L13" s="30"/>
-    </row>
-    <row r="14" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="31" t="str">
-        <f>IF(N3="","Responsible pace — ~0.5–1% per week. This protects muscle and recovery.",IF(OR(N3&lt;-0.01,N3&gt;0.01),"You're changing faster than 1% per week. Adjust your calories a bit.",IF(N3&gt;-0.003,"Little change. Be patient, or adjust your calories slightly.","Responsible pace — ~0.5–1% per week. This protects muscle and recovery.")))</f>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="19" t="n">
+        <f aca="false">SUMIFS('Meal plan'!$E$4:$E$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
+        <v>2220</v>
+      </c>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+    </row>
+    <row r="14" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="20" t="str">
+        <f aca="false">IF(N3="","Responsible pace — ~0.5–1% per week. This protects muscle and recovery.",IF(OR(N3&lt;-0.01,N3&gt;0.01),"You're changing faster than 1% per week. Adjust your calories a bit.",IF(N3&gt;-0.003,"Little change. Be patient, or adjust your calories slightly.","Responsible pace — ~0.5–1% per week. This protects muscle and recovery.")))</f>
         <v>Little change. Be patient, or adjust your calories slightly.</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-    </row>
-    <row r="17" spans="1:12" ht="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+    </row>
+    <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="5"/>
-    </row>
-    <row r="19" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+    </row>
+    <row r="19" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="32" t="s">
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="33" t="s">
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="33"/>
-    </row>
-    <row r="20" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="34">
-        <f>SUMIFS('Meal plan'!$F$4:$F$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
-        <v>155</v>
-      </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="35">
-        <f>SUMIFS('Meal plan'!$G$4:$G$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
-        <v>150</v>
-      </c>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="36">
-        <f>SUMIFS('Meal plan'!$H$4:$H$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
-        <v>56</v>
-      </c>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="23" t="n">
+        <f aca="false">SUMIFS('Meal plan'!$F$4:$F$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
+        <v>148</v>
+      </c>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24" t="n">
+        <f aca="false">SUMIFS('Meal plan'!$G$4:$G$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
+        <v>239</v>
+      </c>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="25" t="n">
+        <f aca="false">SUMIFS('Meal plan'!$H$4:$H$31,'Meal plan'!$A$4:$A$31,$K$8)</f>
+        <v>60</v>
+      </c>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E20:H20"/>
-    <mergeCell ref="I20:L20"/>
-    <mergeCell ref="A16:L16"/>
-    <mergeCell ref="A18:L18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:H19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:F2"/>
+    <mergeCell ref="I1:L2"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J4:L4"/>
     <mergeCell ref="A5:C6"/>
     <mergeCell ref="D5:F6"/>
     <mergeCell ref="G5:I6"/>
@@ -1674,938 +1778,951 @@
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="K8:L8"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:F2"/>
-    <mergeCell ref="I1:L2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="J4:L4"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A18:L18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:L19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:H20"/>
+    <mergeCell ref="I20:L20"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation type="list" sqref="K8" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K8" type="list">
       <formula1>"Mon,Tue,Wed,Thu,Fri,Sat,Sun"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G9:G12" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="G9:G12" type="list">
       <formula1>"✓,—"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFD9D9D9"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="5" max="5" width="7" customWidth="1"/>
-    <col min="6" max="7" width="9" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="9" width="14" hidden="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="0" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="18" t="s">
+      <c r="E3" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="30" t="n">
         <v>640</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G4" s="20">
+      <c r="G4" s="30" t="n">
         <v>82</v>
       </c>
-      <c r="H4" s="20">
+      <c r="H4" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I4" t="str">
-        <f t="shared" ref="I4:I31" si="0">$A4&amp;"|"&amp;$B4</f>
+      <c r="I4" s="0" t="str">
+        <f aca="false">$A4&amp;"|"&amp;$B4</f>
         <v>Mon|Breakfast</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="19" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="20">
+      <c r="E5" s="30" t="n">
         <v>560</v>
       </c>
-      <c r="F5" s="20">
+      <c r="F5" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="G5" s="20">
+      <c r="G5" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="H5" s="20">
+      <c r="H5" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I5" t="str">
-        <f t="shared" si="0"/>
+      <c r="I5" s="0" t="str">
+        <f aca="false">$A5&amp;"|"&amp;$B5</f>
         <v>Mon|Lunch</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="30" t="n">
         <v>720</v>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="30" t="n">
         <v>92</v>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I6" t="str">
-        <f t="shared" si="0"/>
+      <c r="I6" s="0" t="str">
+        <f aca="false">$A6&amp;"|"&amp;$B6</f>
         <v>Mon|Dinner</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="F7" s="20">
+      <c r="F7" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="G7" s="20">
+      <c r="G7" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="H7" s="20">
+      <c r="H7" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I7" t="str">
-        <f t="shared" si="0"/>
+      <c r="I7" s="0" t="str">
+        <f aca="false">$A7&amp;"|"&amp;$B7</f>
         <v>Mon|Snack</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="32" t="n">
         <v>430</v>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="32" t="n">
         <v>42</v>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="str">
-        <f t="shared" si="0"/>
+      <c r="I8" s="0" t="str">
+        <f aca="false">$A8&amp;"|"&amp;$B8</f>
         <v>Tue|Breakfast</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="31" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="32" t="n">
         <v>470</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I9" t="str">
-        <f t="shared" si="0"/>
+      <c r="I9" s="0" t="str">
+        <f aca="false">$A9&amp;"|"&amp;$B9</f>
         <v>Tue|Lunch</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="32" t="n">
         <v>640</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="32" t="n">
         <v>40</v>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="I10" t="str">
-        <f t="shared" si="0"/>
+      <c r="I10" s="0" t="str">
+        <f aca="false">$A10&amp;"|"&amp;$B10</f>
         <v>Tue|Dinner</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="32" t="n">
         <v>280</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="32" t="n">
         <v>32</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="I11" t="str">
-        <f t="shared" si="0"/>
+      <c r="I11" s="0" t="str">
+        <f aca="false">$A11&amp;"|"&amp;$B11</f>
         <v>Tue|Snack</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="19" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="30" t="n">
         <v>76</v>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I12" t="str">
-        <f t="shared" si="0"/>
+      <c r="I12" s="0" t="str">
+        <f aca="false">$A12&amp;"|"&amp;$B12</f>
         <v>Wed|Breakfast</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="19" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="30" t="n">
         <v>45</v>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="I13" t="str">
-        <f t="shared" si="0"/>
+      <c r="I13" s="0" t="str">
+        <f aca="false">$A13&amp;"|"&amp;$B13</f>
         <v>Wed|Lunch</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="19" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="30" t="n">
         <v>740</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="30" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="30" t="n">
         <v>88</v>
       </c>
-      <c r="H14" s="20">
+      <c r="H14" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I14" t="str">
-        <f t="shared" si="0"/>
+      <c r="I14" s="0" t="str">
+        <f aca="false">$A14&amp;"|"&amp;$B14</f>
         <v>Wed|Dinner</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="19" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="30" t="n">
         <v>240</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="30" t="n">
         <v>24</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="str">
-        <f t="shared" si="0"/>
+      <c r="I15" s="0" t="str">
+        <f aca="false">$A15&amp;"|"&amp;$B15</f>
         <v>Wed|Snack</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="22">
+      <c r="E16" s="32" t="n">
         <v>520</v>
       </c>
-      <c r="F16" s="22">
+      <c r="F16" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="32" t="n">
         <v>52</v>
       </c>
-      <c r="H16" s="22">
+      <c r="H16" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="I16" t="str">
-        <f t="shared" si="0"/>
+      <c r="I16" s="0" t="str">
+        <f aca="false">$A16&amp;"|"&amp;$B16</f>
         <v>Thu|Breakfast</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="22">
+      <c r="E17" s="32" t="n">
         <v>560</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="32" t="n">
         <v>48</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="32" t="n">
         <v>55</v>
       </c>
-      <c r="H17" s="22">
+      <c r="H17" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="I17" t="str">
-        <f t="shared" si="0"/>
+      <c r="I17" s="0" t="str">
+        <f aca="false">$A17&amp;"|"&amp;$B17</f>
         <v>Thu|Lunch</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="22">
+      <c r="E18" s="32" t="n">
         <v>600</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="32" t="n">
         <v>42</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="32" t="n">
         <v>62</v>
       </c>
-      <c r="H18" s="22">
+      <c r="H18" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="I18" t="str">
-        <f t="shared" si="0"/>
+      <c r="I18" s="0" t="str">
+        <f aca="false">$A18&amp;"|"&amp;$B18</f>
         <v>Thu|Dinner</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="21" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="32" t="n">
         <v>300</v>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="G19" s="22">
+      <c r="G19" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="H19" s="22">
+      <c r="H19" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I19" t="str">
-        <f t="shared" si="0"/>
+      <c r="I19" s="0" t="str">
+        <f aca="false">$A19&amp;"|"&amp;$B19</f>
         <v>Thu|Snack</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="19" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="30" t="n">
         <v>550</v>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I20" t="str">
-        <f t="shared" si="0"/>
+      <c r="I20" s="0" t="str">
+        <f aca="false">$A20&amp;"|"&amp;$B20</f>
         <v>Fri|Breakfast</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D21" s="19" t="s">
+      <c r="D21" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="30" t="n">
         <v>470</v>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="30" t="n">
         <v>38</v>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" si="0"/>
+      <c r="I21" s="0" t="str">
+        <f aca="false">$A21&amp;"|"&amp;$B21</f>
         <v>Fri|Lunch</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="19" t="s">
+      <c r="B22" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="30" t="n">
         <v>760</v>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="30" t="n">
         <v>40</v>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="30" t="n">
         <v>75</v>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="I22" t="str">
-        <f t="shared" si="0"/>
+      <c r="I22" s="0" t="str">
+        <f aca="false">$A22&amp;"|"&amp;$B22</f>
         <v>Fri|Dinner</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="B23" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="19" t="s">
+      <c r="D23" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="30" t="n">
         <v>280</v>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="30" t="n">
         <v>32</v>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="I23" t="str">
-        <f t="shared" si="0"/>
+      <c r="I23" s="0" t="str">
+        <f aca="false">$A23&amp;"|"&amp;$B23</f>
         <v>Fri|Snack</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="32" t="n">
         <v>480</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="32" t="n">
         <v>38</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="32" t="n">
         <v>46</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="str">
-        <f t="shared" si="0"/>
+      <c r="I24" s="0" t="str">
+        <f aca="false">$A24&amp;"|"&amp;$B24</f>
         <v>Sat|Breakfast</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="32" t="n">
         <v>600</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F25" s="32" t="n">
         <v>45</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G25" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H25" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="I25" t="str">
-        <f t="shared" si="0"/>
+      <c r="I25" s="0" t="str">
+        <f aca="false">$A25&amp;"|"&amp;$B25</f>
         <v>Sat|Lunch</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D26" s="21" t="s">
+      <c r="D26" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="32" t="n">
         <v>620</v>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="32" t="n">
         <v>50</v>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="32" t="n">
         <v>58</v>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I26" t="str">
-        <f t="shared" si="0"/>
+      <c r="I26" s="0" t="str">
+        <f aca="false">$A26&amp;"|"&amp;$B26</f>
         <v>Sat|Dinner</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="32" t="n">
         <v>240</v>
       </c>
-      <c r="F27" s="22">
+      <c r="F27" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="G27" s="22">
+      <c r="G27" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="H27" s="22">
+      <c r="H27" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="str">
-        <f t="shared" si="0"/>
+      <c r="I27" s="0" t="str">
+        <f aca="false">$A27&amp;"|"&amp;$B27</f>
         <v>Sat|Snack</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="19" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D28" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="E28" s="20">
+      <c r="E28" s="30" t="n">
         <v>520</v>
       </c>
-      <c r="F28" s="20">
+      <c r="F28" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="20">
+      <c r="G28" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="H28" s="20">
+      <c r="H28" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I28" t="str">
-        <f t="shared" si="0"/>
+      <c r="I28" s="0" t="str">
+        <f aca="false">$A28&amp;"|"&amp;$B28</f>
         <v>Sun|Breakfast</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="19" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="B29" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="20">
+      <c r="E29" s="30" t="n">
         <v>560</v>
       </c>
-      <c r="F29" s="20">
+      <c r="F29" s="30" t="n">
         <v>48</v>
       </c>
-      <c r="G29" s="20">
+      <c r="G29" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="H29" s="20">
+      <c r="H29" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I29" t="str">
-        <f t="shared" si="0"/>
+      <c r="I29" s="0" t="str">
+        <f aca="false">$A29&amp;"|"&amp;$B29</f>
         <v>Sun|Lunch</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="19" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="20">
+      <c r="E30" s="30" t="n">
         <v>600</v>
       </c>
-      <c r="F30" s="20">
+      <c r="F30" s="30" t="n">
         <v>42</v>
       </c>
-      <c r="G30" s="20">
+      <c r="G30" s="30" t="n">
         <v>62</v>
       </c>
-      <c r="H30" s="20">
+      <c r="H30" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I30" t="str">
-        <f t="shared" si="0"/>
+      <c r="I30" s="0" t="str">
+        <f aca="false">$A30&amp;"|"&amp;$B30</f>
         <v>Sun|Dinner</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="19" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="B31" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E31" s="20">
+      <c r="E31" s="30" t="n">
         <v>300</v>
       </c>
-      <c r="F31" s="20">
+      <c r="F31" s="30" t="n">
         <v>28</v>
       </c>
-      <c r="G31" s="20">
+      <c r="G31" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="H31" s="20">
+      <c r="H31" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I31" t="str">
-        <f t="shared" si="0"/>
+      <c r="I31" s="0" t="str">
+        <f aca="false">$A31&amp;"|"&amp;$B31</f>
         <v>Sun|Snack</v>
       </c>
     </row>
@@ -2614,516 +2731,533 @@
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFD9D9D9"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D30"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="3" width="13" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="28" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="23">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="33" t="n">
         <v>46271</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="34" t="n">
         <v>88.6</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="25"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="23">
+      <c r="C4" s="30"/>
+      <c r="D4" s="35"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="33" t="n">
         <v>46278</v>
       </c>
-      <c r="B5" s="24">
+      <c r="B5" s="34" t="n">
         <v>88.2</v>
       </c>
-      <c r="C5" s="26">
-        <f t="shared" ref="C5:C30" si="0">IF(AND(B5&lt;&gt;"",B4&lt;&gt;""),B5-B4,"")</f>
-        <v>-0.39999999999999147</v>
-      </c>
-      <c r="D5" s="25"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="23">
+      <c r="C5" s="36" t="n">
+        <f aca="false">IF(AND(B5&lt;&gt;"",B4&lt;&gt;""),B5-B4,"")</f>
+        <v>-0.399999999999992</v>
+      </c>
+      <c r="D5" s="35"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="33" t="n">
         <v>46285</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="34" t="n">
         <v>88.4</v>
       </c>
-      <c r="C6" s="26">
-        <f t="shared" si="0"/>
-        <v>0.20000000000000284</v>
-      </c>
-      <c r="D6" s="25"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="23">
+      <c r="C6" s="36" t="n">
+        <f aca="false">IF(AND(B6&lt;&gt;"",B5&lt;&gt;""),B6-B5,"")</f>
+        <v>0.200000000000003</v>
+      </c>
+      <c r="D6" s="35"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="33" t="n">
         <v>46292</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="34" t="n">
         <v>87.9</v>
       </c>
-      <c r="C7" s="26">
-        <f t="shared" si="0"/>
+      <c r="C7" s="36" t="n">
+        <f aca="false">IF(AND(B7&lt;&gt;"",B6&lt;&gt;""),B7-B6,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D7" s="25"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="23">
+      <c r="D7" s="35"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="33" t="n">
         <v>46299</v>
       </c>
-      <c r="B8" s="24">
+      <c r="B8" s="34" t="n">
         <v>87.6</v>
       </c>
-      <c r="C8" s="26">
-        <f t="shared" si="0"/>
-        <v>-0.30000000000001137</v>
-      </c>
-      <c r="D8" s="25"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="23">
+      <c r="C8" s="36" t="n">
+        <f aca="false">IF(AND(B8&lt;&gt;"",B7&lt;&gt;""),B8-B7,"")</f>
+        <v>-0.300000000000011</v>
+      </c>
+      <c r="D8" s="35"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="33" t="n">
         <v>46306</v>
       </c>
-      <c r="B9" s="24">
+      <c r="B9" s="34" t="n">
         <v>87.7</v>
       </c>
-      <c r="C9" s="26">
-        <f t="shared" si="0"/>
-        <v>0.10000000000000853</v>
-      </c>
-      <c r="D9" s="25"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="23">
+      <c r="C9" s="36" t="n">
+        <f aca="false">IF(AND(B9&lt;&gt;"",B8&lt;&gt;""),B9-B8,"")</f>
+        <v>0.100000000000009</v>
+      </c>
+      <c r="D9" s="35"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="33" t="n">
         <v>46313</v>
       </c>
-      <c r="B10" s="24">
+      <c r="B10" s="34" t="n">
         <v>87.2</v>
       </c>
-      <c r="C10" s="26">
-        <f t="shared" si="0"/>
+      <c r="C10" s="36" t="n">
+        <f aca="false">IF(AND(B10&lt;&gt;"",B9&lt;&gt;""),B10-B9,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D10" s="25"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="23">
+      <c r="D10" s="35"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="33" t="n">
         <v>46320</v>
       </c>
-      <c r="B11" s="24">
+      <c r="B11" s="34" t="n">
         <v>87</v>
       </c>
-      <c r="C11" s="26">
-        <f t="shared" si="0"/>
-        <v>-0.20000000000000284</v>
-      </c>
-      <c r="D11" s="25"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="20"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="C11" s="36" t="n">
+        <f aca="false">IF(AND(B11&lt;&gt;"",B10&lt;&gt;""),B11-B10,"")</f>
+        <v>-0.200000000000003</v>
+      </c>
+      <c r="D11" s="35"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="30"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="36" t="str">
+        <f aca="false">IF(AND(B12&lt;&gt;"",B11&lt;&gt;""),B12-B11,"")</f>
         <v/>
       </c>
-      <c r="D12" s="25"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="20"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D12" s="35"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="36" t="str">
+        <f aca="false">IF(AND(B13&lt;&gt;"",B12&lt;&gt;""),B13-B12,"")</f>
         <v/>
       </c>
-      <c r="D13" s="25"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="20"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D13" s="35"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="30"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="36" t="str">
+        <f aca="false">IF(AND(B14&lt;&gt;"",B13&lt;&gt;""),B14-B13,"")</f>
         <v/>
       </c>
-      <c r="D14" s="25"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D14" s="35"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="36" t="str">
+        <f aca="false">IF(AND(B15&lt;&gt;"",B14&lt;&gt;""),B15-B14,"")</f>
         <v/>
       </c>
-      <c r="D15" s="25"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="20"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D15" s="35"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="30"/>
+      <c r="B16" s="34"/>
+      <c r="C16" s="36" t="str">
+        <f aca="false">IF(AND(B16&lt;&gt;"",B15&lt;&gt;""),B16-B15,"")</f>
         <v/>
       </c>
-      <c r="D16" s="25"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="20"/>
-      <c r="B17" s="24"/>
-      <c r="C17" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D16" s="35"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="36" t="str">
+        <f aca="false">IF(AND(B17&lt;&gt;"",B16&lt;&gt;""),B17-B16,"")</f>
         <v/>
       </c>
-      <c r="D17" s="25"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="20"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D17" s="35"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="30"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="36" t="str">
+        <f aca="false">IF(AND(B18&lt;&gt;"",B17&lt;&gt;""),B18-B17,"")</f>
         <v/>
       </c>
-      <c r="D18" s="25"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="20"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D18" s="35"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30"/>
+      <c r="B19" s="34"/>
+      <c r="C19" s="36" t="str">
+        <f aca="false">IF(AND(B19&lt;&gt;"",B18&lt;&gt;""),B19-B18,"")</f>
         <v/>
       </c>
-      <c r="D19" s="25"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="20"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D19" s="35"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="30"/>
+      <c r="B20" s="34"/>
+      <c r="C20" s="36" t="str">
+        <f aca="false">IF(AND(B20&lt;&gt;"",B19&lt;&gt;""),B20-B19,"")</f>
         <v/>
       </c>
-      <c r="D20" s="25"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="20"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D20" s="35"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30"/>
+      <c r="B21" s="34"/>
+      <c r="C21" s="36" t="str">
+        <f aca="false">IF(AND(B21&lt;&gt;"",B20&lt;&gt;""),B21-B20,"")</f>
         <v/>
       </c>
-      <c r="D21" s="25"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="20"/>
-      <c r="B22" s="24"/>
-      <c r="C22" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D21" s="35"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="30"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="36" t="str">
+        <f aca="false">IF(AND(B22&lt;&gt;"",B21&lt;&gt;""),B22-B21,"")</f>
         <v/>
       </c>
-      <c r="D22" s="25"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="20"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D22" s="35"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="36" t="str">
+        <f aca="false">IF(AND(B23&lt;&gt;"",B22&lt;&gt;""),B23-B22,"")</f>
         <v/>
       </c>
-      <c r="D23" s="25"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="20"/>
-      <c r="B24" s="24"/>
-      <c r="C24" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D23" s="35"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="30"/>
+      <c r="B24" s="34"/>
+      <c r="C24" s="36" t="str">
+        <f aca="false">IF(AND(B24&lt;&gt;"",B23&lt;&gt;""),B24-B23,"")</f>
         <v/>
       </c>
-      <c r="D24" s="25"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="20"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D24" s="35"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="36" t="str">
+        <f aca="false">IF(AND(B25&lt;&gt;"",B24&lt;&gt;""),B25-B24,"")</f>
         <v/>
       </c>
-      <c r="D25" s="25"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="20"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D25" s="35"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="30"/>
+      <c r="B26" s="34"/>
+      <c r="C26" s="36" t="str">
+        <f aca="false">IF(AND(B26&lt;&gt;"",B25&lt;&gt;""),B26-B25,"")</f>
         <v/>
       </c>
-      <c r="D26" s="25"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="20"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D26" s="35"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30"/>
+      <c r="B27" s="34"/>
+      <c r="C27" s="36" t="str">
+        <f aca="false">IF(AND(B27&lt;&gt;"",B26&lt;&gt;""),B27-B26,"")</f>
         <v/>
       </c>
-      <c r="D27" s="25"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="20"/>
-      <c r="B28" s="24"/>
-      <c r="C28" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D27" s="35"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="30"/>
+      <c r="B28" s="34"/>
+      <c r="C28" s="36" t="str">
+        <f aca="false">IF(AND(B28&lt;&gt;"",B27&lt;&gt;""),B28-B27,"")</f>
         <v/>
       </c>
-      <c r="D28" s="25"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="20"/>
-      <c r="B29" s="24"/>
-      <c r="C29" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D28" s="35"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="36" t="str">
+        <f aca="false">IF(AND(B29&lt;&gt;"",B28&lt;&gt;""),B29-B28,"")</f>
         <v/>
       </c>
-      <c r="D29" s="25"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="20"/>
-      <c r="B30" s="24"/>
-      <c r="C30" s="26" t="str">
-        <f t="shared" si="0"/>
+      <c r="D29" s="35"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="30"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="36" t="str">
+        <f aca="false">IF(AND(B30&lt;&gt;"",B29&lt;&gt;""),B30-B29,"")</f>
         <v/>
       </c>
-      <c r="D30" s="25"/>
+      <c r="D30" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
     <tabColor rgb="FFD9D9D9"/>
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.2" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="37"/>
-      <c r="C1" s="37"/>
-      <c r="D1" s="37"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="18" t="s">
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="18" t="s">
+      <c r="C3" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="28" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="C4" s="38"/>
+      <c r="D4" s="39"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="27" t="s">
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="27" t="s">
+      <c r="C6" s="38"/>
+      <c r="D6" s="39"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="37" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="29" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="27" t="s">
+      <c r="C7" s="38"/>
+      <c r="D7" s="39"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="29" t="s">
         <v>77</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="C8" s="38"/>
+      <c r="D8" s="39"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="C9" s="38"/>
+      <c r="D9" s="39"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="27" t="s">
+      <c r="C10" s="38"/>
+      <c r="D10" s="39"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="C11" s="38"/>
+      <c r="D11" s="39"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="29"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="27" t="s">
+      <c r="C12" s="38"/>
+      <c r="D12" s="39"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="B13" s="19" t="s">
+      <c r="B13" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="28"/>
-      <c r="D13" s="29"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
+      <c r="C13" s="38"/>
+      <c r="D13" s="39"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="19" t="s">
+      <c r="B14" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="27" t="s">
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="29"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="29"/>
+      <c r="C16" s="38"/>
+      <c r="D16" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/tracker-en.xlsx
+++ b/tracker-en.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Meal plan" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Weight" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Shopping" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Recipes" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="228">
   <si>
     <t xml:space="preserve">H</t>
   </si>
@@ -287,25 +288,444 @@
   </si>
   <si>
     <t xml:space="preserve">Pasta 500g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RECIPES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 chef-built recipes with macros and method. Macros are estimates for the amounts shown.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Savoury Oats with Egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast · Fibermaxxing / Recovery   —   420 kcal · 22g P · 42g C · 16g F · 9g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INGREDIENTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low-fat stock</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fresh spinach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egg (poached)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (50 g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pumpkin seeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">METHOD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bring the stock to a gentle simmer in a small pan.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stir in the oats and cook 4–5 min, stirring, until creamy.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fold through the spinach in the last minute until just wilted; season.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meanwhile poach the egg ~3 min in simmering water with a splash of vinegar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoon the oats into a bowl, top with the egg, scatter the pumpkin seeds and a crack of pepper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vegan Lentil-Chickpea Curry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner · Plant-based / Muscle gain   —   510 kcal · 26g P · 58g C · 15g F · 14g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lentils (tinned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chickpeas (tinned)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chopped tomatoes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light coconut milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curry spices</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warm a dash of oil in a pan and toast the curry spices ~30 sec until fragrant.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the chopped tomatoes and simmer 3–4 min to reduce slightly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stir in the drained lentils and chickpeas; simmer 5 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour in the coconut milk, add the kale, and cook 2–3 min until the kale softens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Season with salt; finish with lemon or coriander. Serve as is or with rice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matcha Protein Overnight Oats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast · Focus / Pre-workout   —   460 kcal · 32g P · 48g C · 12g F · 8g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vanilla protein powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matcha powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chia seeds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almond milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In a jar, whisk the almond milk with the protein powder and matcha until smooth.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stir in the oats and chia seeds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal and refrigerate overnight (minimum 4 hours).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the morning, stir and loosen with a splash of milk if thick. Top with fruit if you like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmon &amp; Quinoa Clean Bowl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner · Clean label / Omega-3   —   580 kcal · 38g P · 45g C · 22g F · 7g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quinoa (dry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmon fillet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoli (steamed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Edamame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive oil + lemon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rinse the quinoa and simmer in twice its volume of water 12–15 min until fluffy; rest covered.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Season the salmon and pan-sear skin-side down 3–4 min, then flip for 2 min (or bake at 200°C ~12 min).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steam the broccoli and edamame 4–5 min until bright and just tender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whisk the olive oil with the lemon juice, salt and pepper.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build the bowl with quinoa, broccoli and edamame; flake over the salmon and dress.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempeh &amp; Broccoli Stir-Fry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner · Plant-based / Gut health   —   490 kcal · 28g P · 35g C · 21g F · 10g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tempeh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Broccoli florets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bell pepper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brown rice (dry)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tamari, ginger, garlic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cook the brown rice (simmer ~25 min) and keep warm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cube the tempeh and sear in a hot pan with a little oil until golden on all sides.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the broccoli and pepper; stir-fry 4–5 min, adding a splash of water to steam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add grated ginger and garlic for 30 sec, then the tamari, and toss to coat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serve over the brown rice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashwagandha Recovery Shake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack · Adaptogens / Calm   —   340 kcal · 26g P · 28g C · 8g F · 6g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frozen banana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Protein powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">250 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Almond butter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ashwagandha powder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add everything to a blender.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blend 30–45 sec until smooth and thick.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loosen with more milk or thicken with ice to taste. Drink fresh.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage Cheese &amp; Avocado Toast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast · Quick protein / Healthy fats   —   390 kcal · 24g P · 30g C · 17g F · 8g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wholegrain / sourdough bread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cottage cheese</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avocado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chilli, pepper, salt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">to taste</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toast the bread to your liking.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spread the cottage cheese over the warm toast.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fork-mash or slice the avocado on top.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Finish with chilli flakes, salt and pepper, and a squeeze of lemon if you like.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicken &amp; Sweet Potato Traybake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dinner · Clean label / Endurance   —   540 kcal · 42g P · 52g C · 12g F · 8g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chicken breast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweet potato</t>
+  </si>
+  <si>
+    <t xml:space="preserve">200 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asparagus tips</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olive oil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paprika, salt, rosemary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat the oven to 200°C. Cube the sweet potato and toss with half the oil, paprika and salt.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roast the sweet potato on a tray for 15 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rub the chicken with the rest of the oil and the rosemary; add to the tray and roast 15 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add the asparagus and roast a final 8–10 min, until the chicken reaches 74°C.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest 3 min, then serve.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chia Pudding with Blueberries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Snack · Fibermaxxing / Antioxidants   —   310 kcal · 15g P · 22g C · 14g F · 11g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lupin flour / protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plant milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blueberries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cinnamon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whisk the plant milk with the lupin flour / protein powder and cinnamon.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stir in the chia seeds; wait 5 min and stir again to stop clumping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refrigerate 2 hours or overnight until set.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top with the blueberries before serving.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High-Protein Pancakes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakfast · Muscle recovery / Classic   —   430 kcal · 35g P · 38g C · 9g F · 5g fibre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oat flour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whey or pea protein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Egg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skimmed milk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whisk the oat flour, protein powder, egg and milk into a smooth batter; rest 5 min.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heat a non-stick pan over medium with a little spray oil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pour small pancakes; cook until bubbles form (~1–2 min), flip, and cook 1 min more.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack and top with fruit or yoghurt if you like.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-    <numFmt numFmtId="166" formatCode="0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="167" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
-    <numFmt numFmtId="168" formatCode="#,##0&quot; kcal&quot;"/>
-    <numFmt numFmtId="169" formatCode="#,##0"/>
-    <numFmt numFmtId="170" formatCode="0&quot; g&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="166" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot; kcal&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0"/>
+    <numFmt numFmtId="169" formatCode="0&quot; g&quot;"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="mm\-dd\-yyyy"/>
-    <numFmt numFmtId="172" formatCode="0.0"/>
-    <numFmt numFmtId="173" formatCode="\+0.0;\-0.0"/>
+    <numFmt numFmtId="172" formatCode="\+0.0;\-0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -485,6 +905,59 @@
     <font>
       <sz val="10"/>
       <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFE8321E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF404040"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -724,8 +1197,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -741,10 +1218,6 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -753,11 +1226,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -765,15 +1238,15 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -793,7 +1266,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -801,7 +1274,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -817,23 +1290,23 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -841,7 +1314,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -849,7 +1322,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="7" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -861,7 +1334,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -869,20 +1342,60 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -947,11 +1460,11 @@
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF1F9D55"/>
       <rgbColor rgb="FF0A0A0A"/>
-      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF444444"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF444444"/>
+      <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -997,22 +1510,26 @@
           </c:marker>
           <c:dLbls>
             <c:txPr>
-              <a:bodyPr wrap="none"/>
+              <a:bodyPr wrap="square"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
-            <c:separator> </c:separator>
+            <c:separator>; </c:separator>
             <c:showLeaderLines val="1"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
@@ -1152,17 +1669,17 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="63125726"/>
-        <c:axId val="36317127"/>
+        <c:axId val="83911378"/>
+        <c:axId val="45546000"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="63125726"/>
+        <c:axId val="83911378"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:numFmt formatCode="mm\-dd\-yyyy" sourceLinked="1"/>
+        <c:numFmt formatCode="mm\-dd\-yyyy" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1188,7 +1705,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36317127"/>
+        <c:crossAx val="45546000"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1196,13 +1713,13 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36317127"/>
+        <c:axId val="45546000"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1228,7 +1745,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63125726"/>
+        <c:crossAx val="83911378"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1267,9 +1784,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>78120</xdr:colOff>
+      <xdr:colOff>77760</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>97920</xdr:rowOff>
+      <xdr:rowOff>97560</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1278,7 +1795,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="1743120"/>
-        <a:ext cx="4139640" cy="1907640"/>
+        <a:ext cx="4139280" cy="1907280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1475,50 +1992,50 @@
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="0" width="9.6"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="1" style="1" width="9.6"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="14" min="14" style="1" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="I1" s="3" t="s">
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="I1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="N1" s="4" t="n">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="N1" s="1" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(Weight!$B$4:$B$30&lt;&gt;""),Weight!$B$4:$B$30),"")</f>
         <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="N2" s="4" t="n">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="N2" s="1" t="n">
         <f aca="false">IFERROR(LOOKUP(2,1/(Weight!$C$4:$C$30&lt;&gt;""),Weight!$C$4:$C$30),"")</f>
         <v>-0.200000000000003</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="N3" s="0" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="N3" s="1" t="n">
         <f aca="false">IF(AND(N1&lt;&gt;"",N2&lt;&gt;""),N2/N1,"")</f>
         <v>-0.00229885057471268</v>
       </c>
@@ -1586,7 +2103,7 @@
       <c r="L6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="11" t="s">
         <v>7</v>
       </c>
@@ -1703,7 +2220,7 @@
       <c r="L16" s="20"/>
     </row>
     <row r="17" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
         <v>15</v>
       </c>
@@ -1823,17 +2340,17 @@
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="9" min="9" style="1" width="14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
         <v>19</v>
       </c>
@@ -1845,7 +2362,7 @@
       <c r="G1" s="26"/>
       <c r="H1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
         <v>20</v>
       </c>
@@ -1857,7 +2374,7 @@
       <c r="G2" s="27"/>
       <c r="H2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>21</v>
       </c>
@@ -1882,11 +2399,11 @@
       <c r="H3" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
         <v>9</v>
       </c>
@@ -1911,12 +2428,12 @@
       <c r="H4" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I4" s="0" t="str">
+      <c r="I4" s="1" t="str">
         <f aca="false">$A4&amp;"|"&amp;$B4</f>
         <v>Mon|Breakfast</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
@@ -1941,12 +2458,12 @@
       <c r="H5" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I5" s="0" t="str">
+      <c r="I5" s="1" t="str">
         <f aca="false">$A5&amp;"|"&amp;$B5</f>
         <v>Mon|Lunch</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
         <v>9</v>
       </c>
@@ -1971,12 +2488,12 @@
       <c r="H6" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I6" s="0" t="str">
+      <c r="I6" s="1" t="str">
         <f aca="false">$A6&amp;"|"&amp;$B6</f>
         <v>Mon|Dinner</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="29" t="s">
         <v>9</v>
       </c>
@@ -2001,12 +2518,12 @@
       <c r="H7" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I7" s="0" t="str">
+      <c r="I7" s="1" t="str">
         <f aca="false">$A7&amp;"|"&amp;$B7</f>
         <v>Mon|Snack</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="31" t="s">
         <v>38</v>
       </c>
@@ -2031,12 +2548,12 @@
       <c r="H8" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="I8" s="0" t="str">
+      <c r="I8" s="1" t="str">
         <f aca="false">$A8&amp;"|"&amp;$B8</f>
         <v>Tue|Breakfast</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="31" t="s">
         <v>38</v>
       </c>
@@ -2061,12 +2578,12 @@
       <c r="H9" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="0" t="str">
+      <c r="I9" s="1" t="str">
         <f aca="false">$A9&amp;"|"&amp;$B9</f>
         <v>Tue|Lunch</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="31" t="s">
         <v>38</v>
       </c>
@@ -2091,12 +2608,12 @@
       <c r="H10" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="I10" s="0" t="str">
+      <c r="I10" s="1" t="str">
         <f aca="false">$A10&amp;"|"&amp;$B10</f>
         <v>Tue|Dinner</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="31" t="s">
         <v>38</v>
       </c>
@@ -2121,12 +2638,12 @@
       <c r="H11" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="I11" s="0" t="str">
+      <c r="I11" s="1" t="str">
         <f aca="false">$A11&amp;"|"&amp;$B11</f>
         <v>Tue|Snack</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="29" t="s">
         <v>47</v>
       </c>
@@ -2151,12 +2668,12 @@
       <c r="H12" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I12" s="0" t="str">
+      <c r="I12" s="1" t="str">
         <f aca="false">$A12&amp;"|"&amp;$B12</f>
         <v>Wed|Breakfast</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="29" t="s">
         <v>47</v>
       </c>
@@ -2181,12 +2698,12 @@
       <c r="H13" s="30" t="n">
         <v>30</v>
       </c>
-      <c r="I13" s="0" t="str">
+      <c r="I13" s="1" t="str">
         <f aca="false">$A13&amp;"|"&amp;$B13</f>
         <v>Wed|Lunch</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="29" t="s">
         <v>47</v>
       </c>
@@ -2211,12 +2728,12 @@
       <c r="H14" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I14" s="0" t="str">
+      <c r="I14" s="1" t="str">
         <f aca="false">$A14&amp;"|"&amp;$B14</f>
         <v>Wed|Dinner</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="29" t="s">
         <v>47</v>
       </c>
@@ -2241,12 +2758,12 @@
       <c r="H15" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="I15" s="0" t="str">
+      <c r="I15" s="1" t="str">
         <f aca="false">$A15&amp;"|"&amp;$B15</f>
         <v>Wed|Snack</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="31" t="s">
         <v>56</v>
       </c>
@@ -2271,12 +2788,12 @@
       <c r="H16" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="I16" s="0" t="str">
+      <c r="I16" s="1" t="str">
         <f aca="false">$A16&amp;"|"&amp;$B16</f>
         <v>Thu|Breakfast</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="31" t="s">
         <v>56</v>
       </c>
@@ -2301,12 +2818,12 @@
       <c r="H17" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="I17" s="0" t="str">
+      <c r="I17" s="1" t="str">
         <f aca="false">$A17&amp;"|"&amp;$B17</f>
         <v>Thu|Lunch</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="31" t="s">
         <v>56</v>
       </c>
@@ -2331,12 +2848,12 @@
       <c r="H18" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="I18" s="0" t="str">
+      <c r="I18" s="1" t="str">
         <f aca="false">$A18&amp;"|"&amp;$B18</f>
         <v>Thu|Dinner</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="31" t="s">
         <v>56</v>
       </c>
@@ -2361,12 +2878,12 @@
       <c r="H19" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I19" s="0" t="str">
+      <c r="I19" s="1" t="str">
         <f aca="false">$A19&amp;"|"&amp;$B19</f>
         <v>Thu|Snack</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="29" t="s">
         <v>57</v>
       </c>
@@ -2391,12 +2908,12 @@
       <c r="H20" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="I20" s="0" t="str">
+      <c r="I20" s="1" t="str">
         <f aca="false">$A20&amp;"|"&amp;$B20</f>
         <v>Fri|Breakfast</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="29" t="s">
         <v>57</v>
       </c>
@@ -2421,12 +2938,12 @@
       <c r="H21" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="I21" s="0" t="str">
+      <c r="I21" s="1" t="str">
         <f aca="false">$A21&amp;"|"&amp;$B21</f>
         <v>Fri|Lunch</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
         <v>57</v>
       </c>
@@ -2451,12 +2968,12 @@
       <c r="H22" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="I22" s="0" t="str">
+      <c r="I22" s="1" t="str">
         <f aca="false">$A22&amp;"|"&amp;$B22</f>
         <v>Fri|Dinner</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="29" t="s">
         <v>57</v>
       </c>
@@ -2481,12 +2998,12 @@
       <c r="H23" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="I23" s="0" t="str">
+      <c r="I23" s="1" t="str">
         <f aca="false">$A23&amp;"|"&amp;$B23</f>
         <v>Fri|Snack</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="31" t="s">
         <v>58</v>
       </c>
@@ -2511,12 +3028,12 @@
       <c r="H24" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="I24" s="0" t="str">
+      <c r="I24" s="1" t="str">
         <f aca="false">$A24&amp;"|"&amp;$B24</f>
         <v>Sat|Breakfast</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="31" t="s">
         <v>58</v>
       </c>
@@ -2541,12 +3058,12 @@
       <c r="H25" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="I25" s="0" t="str">
+      <c r="I25" s="1" t="str">
         <f aca="false">$A25&amp;"|"&amp;$B25</f>
         <v>Sat|Lunch</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="31" t="s">
         <v>58</v>
       </c>
@@ -2571,12 +3088,12 @@
       <c r="H26" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="I26" s="0" t="str">
+      <c r="I26" s="1" t="str">
         <f aca="false">$A26&amp;"|"&amp;$B26</f>
         <v>Sat|Dinner</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="31" t="s">
         <v>58</v>
       </c>
@@ -2601,12 +3118,12 @@
       <c r="H27" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="I27" s="0" t="str">
+      <c r="I27" s="1" t="str">
         <f aca="false">$A27&amp;"|"&amp;$B27</f>
         <v>Sat|Snack</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="29" t="s">
         <v>59</v>
       </c>
@@ -2631,12 +3148,12 @@
       <c r="H28" s="30" t="n">
         <v>18</v>
       </c>
-      <c r="I28" s="0" t="str">
+      <c r="I28" s="1" t="str">
         <f aca="false">$A28&amp;"|"&amp;$B28</f>
         <v>Sun|Breakfast</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="29" t="s">
         <v>59</v>
       </c>
@@ -2661,12 +3178,12 @@
       <c r="H29" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="I29" s="0" t="str">
+      <c r="I29" s="1" t="str">
         <f aca="false">$A29&amp;"|"&amp;$B29</f>
         <v>Sun|Lunch</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="29" t="s">
         <v>59</v>
       </c>
@@ -2691,12 +3208,12 @@
       <c r="H30" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="I30" s="0" t="str">
+      <c r="I30" s="1" t="str">
         <f aca="false">$A30&amp;"|"&amp;$B30</f>
         <v>Sun|Dinner</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="29" t="s">
         <v>59</v>
       </c>
@@ -2721,7 +3238,7 @@
       <c r="H31" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="I31" s="0" t="str">
+      <c r="I31" s="1" t="str">
         <f aca="false">$A31&amp;"|"&amp;$B31</f>
         <v>Sun|Snack</v>
       </c>
@@ -2750,12 +3267,12 @@
   <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
         <v>60</v>
       </c>
@@ -2763,7 +3280,7 @@
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
         <v>61</v>
       </c>
@@ -2771,7 +3288,7 @@
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>62</v>
       </c>
@@ -2785,7 +3302,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="33" t="n">
         <v>46271</v>
       </c>
@@ -2795,7 +3312,7 @@
       <c r="C4" s="30"/>
       <c r="D4" s="35"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="n">
         <v>46278</v>
       </c>
@@ -2808,7 +3325,7 @@
       </c>
       <c r="D5" s="35"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="33" t="n">
         <v>46285</v>
       </c>
@@ -2821,7 +3338,7 @@
       </c>
       <c r="D6" s="35"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="33" t="n">
         <v>46292</v>
       </c>
@@ -2834,7 +3351,7 @@
       </c>
       <c r="D7" s="35"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="33" t="n">
         <v>46299</v>
       </c>
@@ -2847,7 +3364,7 @@
       </c>
       <c r="D8" s="35"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="33" t="n">
         <v>46306</v>
       </c>
@@ -2860,7 +3377,7 @@
       </c>
       <c r="D9" s="35"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="33" t="n">
         <v>46313</v>
       </c>
@@ -2873,7 +3390,7 @@
       </c>
       <c r="D10" s="35"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="33" t="n">
         <v>46320</v>
       </c>
@@ -2886,7 +3403,7 @@
       </c>
       <c r="D11" s="35"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30"/>
       <c r="B12" s="34"/>
       <c r="C12" s="36" t="str">
@@ -2895,7 +3412,7 @@
       </c>
       <c r="D12" s="35"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30"/>
       <c r="B13" s="34"/>
       <c r="C13" s="36" t="str">
@@ -2904,7 +3421,7 @@
       </c>
       <c r="D13" s="35"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30"/>
       <c r="B14" s="34"/>
       <c r="C14" s="36" t="str">
@@ -2913,7 +3430,7 @@
       </c>
       <c r="D14" s="35"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30"/>
       <c r="B15" s="34"/>
       <c r="C15" s="36" t="str">
@@ -2922,7 +3439,7 @@
       </c>
       <c r="D15" s="35"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30"/>
       <c r="B16" s="34"/>
       <c r="C16" s="36" t="str">
@@ -2931,7 +3448,7 @@
       </c>
       <c r="D16" s="35"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30"/>
       <c r="B17" s="34"/>
       <c r="C17" s="36" t="str">
@@ -2940,7 +3457,7 @@
       </c>
       <c r="D17" s="35"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30"/>
       <c r="B18" s="34"/>
       <c r="C18" s="36" t="str">
@@ -2949,7 +3466,7 @@
       </c>
       <c r="D18" s="35"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30"/>
       <c r="B19" s="34"/>
       <c r="C19" s="36" t="str">
@@ -2958,7 +3475,7 @@
       </c>
       <c r="D19" s="35"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="30"/>
       <c r="B20" s="34"/>
       <c r="C20" s="36" t="str">
@@ -2967,7 +3484,7 @@
       </c>
       <c r="D20" s="35"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30"/>
       <c r="B21" s="34"/>
       <c r="C21" s="36" t="str">
@@ -2976,7 +3493,7 @@
       </c>
       <c r="D21" s="35"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="30"/>
       <c r="B22" s="34"/>
       <c r="C22" s="36" t="str">
@@ -2985,7 +3502,7 @@
       </c>
       <c r="D22" s="35"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30"/>
       <c r="B23" s="34"/>
       <c r="C23" s="36" t="str">
@@ -2994,7 +3511,7 @@
       </c>
       <c r="D23" s="35"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30"/>
       <c r="B24" s="34"/>
       <c r="C24" s="36" t="str">
@@ -3003,7 +3520,7 @@
       </c>
       <c r="D24" s="35"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="30"/>
       <c r="B25" s="34"/>
       <c r="C25" s="36" t="str">
@@ -3012,7 +3529,7 @@
       </c>
       <c r="D25" s="35"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="30"/>
       <c r="B26" s="34"/>
       <c r="C26" s="36" t="str">
@@ -3021,7 +3538,7 @@
       </c>
       <c r="D26" s="35"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="30"/>
       <c r="B27" s="34"/>
       <c r="C27" s="36" t="str">
@@ -3030,7 +3547,7 @@
       </c>
       <c r="D27" s="35"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30"/>
       <c r="B28" s="34"/>
       <c r="C28" s="36" t="str">
@@ -3039,7 +3556,7 @@
       </c>
       <c r="D28" s="35"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="30"/>
       <c r="B29" s="34"/>
       <c r="C29" s="36" t="str">
@@ -3048,7 +3565,7 @@
       </c>
       <c r="D29" s="35"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30"/>
       <c r="B30" s="34"/>
       <c r="C30" s="36" t="str">
@@ -3081,13 +3598,13 @@
   <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
         <v>66</v>
       </c>
@@ -3095,7 +3612,7 @@
       <c r="C1" s="26"/>
       <c r="D1" s="26"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
         <v>67</v>
       </c>
@@ -3103,7 +3620,7 @@
       <c r="C2" s="27"/>
       <c r="D2" s="27"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
         <v>68</v>
       </c>
@@ -3117,7 +3634,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="37" t="s">
         <v>72</v>
       </c>
@@ -3127,7 +3644,7 @@
       <c r="C4" s="38"/>
       <c r="D4" s="39"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37" t="s">
         <v>72</v>
       </c>
@@ -3137,7 +3654,7 @@
       <c r="C5" s="38"/>
       <c r="D5" s="39"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="37" t="s">
         <v>72</v>
       </c>
@@ -3147,7 +3664,7 @@
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="37" t="s">
         <v>72</v>
       </c>
@@ -3157,7 +3674,7 @@
       <c r="C7" s="38"/>
       <c r="D7" s="39"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="37" t="s">
         <v>16</v>
       </c>
@@ -3167,7 +3684,7 @@
       <c r="C8" s="38"/>
       <c r="D8" s="39"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="37" t="s">
         <v>16</v>
       </c>
@@ -3177,7 +3694,7 @@
       <c r="C9" s="38"/>
       <c r="D9" s="39"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="37" t="s">
         <v>16</v>
       </c>
@@ -3187,7 +3704,7 @@
       <c r="C10" s="38"/>
       <c r="D10" s="39"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="37" t="s">
         <v>80</v>
       </c>
@@ -3197,7 +3714,7 @@
       <c r="C11" s="38"/>
       <c r="D11" s="39"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="37" t="s">
         <v>80</v>
       </c>
@@ -3207,7 +3724,7 @@
       <c r="C12" s="38"/>
       <c r="D12" s="39"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="37" t="s">
         <v>80</v>
       </c>
@@ -3217,7 +3734,7 @@
       <c r="C13" s="38"/>
       <c r="D13" s="39"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="37" t="s">
         <v>84</v>
       </c>
@@ -3227,7 +3744,7 @@
       <c r="C14" s="38"/>
       <c r="D14" s="39"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="37" t="s">
         <v>84</v>
       </c>
@@ -3237,7 +3754,7 @@
       <c r="C15" s="38"/>
       <c r="D15" s="39"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="37" t="s">
         <v>84</v>
       </c>
@@ -3260,4 +3777,1319 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D145"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="40" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="41" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="46"/>
+      <c r="D7" s="47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="46"/>
+      <c r="D8" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="C9" s="46"/>
+      <c r="D9" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="D10" s="47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="46"/>
+      <c r="D11" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" s="49"/>
+      <c r="D15" s="49"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="42" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="B20" s="44"/>
+      <c r="C20" s="44"/>
+      <c r="D20" s="44"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C22" s="46"/>
+      <c r="D22" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C23" s="46"/>
+      <c r="D23" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="C24" s="46"/>
+      <c r="D24" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="46"/>
+      <c r="D25" s="47" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C26" s="46"/>
+      <c r="D26" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="46" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="46"/>
+      <c r="D27" s="47" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>123</v>
+      </c>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="49" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="43" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="B36" s="44"/>
+      <c r="C36" s="44"/>
+      <c r="D36" s="44"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C38" s="46"/>
+      <c r="D38" s="47" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C39" s="46"/>
+      <c r="D39" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="46"/>
+      <c r="D40" s="47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="46"/>
+      <c r="D41" s="47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C42" s="46"/>
+      <c r="D42" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="49" t="s">
+        <v>135</v>
+      </c>
+      <c r="C44" s="49"/>
+      <c r="D44" s="49"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="49" t="s">
+        <v>136</v>
+      </c>
+      <c r="C45" s="49"/>
+      <c r="D45" s="49"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="49" t="s">
+        <v>137</v>
+      </c>
+      <c r="C46" s="49"/>
+      <c r="D46" s="49"/>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="43" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="B50" s="44"/>
+      <c r="C50" s="44"/>
+      <c r="D50" s="44"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="46"/>
+      <c r="D52" s="47" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="46"/>
+      <c r="D53" s="47" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C54" s="46"/>
+      <c r="D54" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55" s="46"/>
+      <c r="D55" s="47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" s="46"/>
+      <c r="D56" s="47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="C58" s="49"/>
+      <c r="D58" s="49"/>
+    </row>
+    <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="49" t="s">
+        <v>149</v>
+      </c>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" s="49"/>
+      <c r="D60" s="49"/>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="49" t="s">
+        <v>151</v>
+      </c>
+      <c r="C61" s="49"/>
+      <c r="D61" s="49"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="49" t="s">
+        <v>152</v>
+      </c>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+    </row>
+    <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="43" t="s">
+        <v>153</v>
+      </c>
+      <c r="C64" s="43"/>
+      <c r="D64" s="43"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B65" s="44"/>
+      <c r="C65" s="44"/>
+      <c r="D65" s="44"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" s="46"/>
+      <c r="D67" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="46"/>
+      <c r="D68" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="C69" s="46"/>
+      <c r="D69" s="47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C70" s="46"/>
+      <c r="D70" s="47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="C71" s="46"/>
+      <c r="D71" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="49" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" s="49"/>
+      <c r="D73" s="49"/>
+    </row>
+    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" s="49" t="s">
+        <v>163</v>
+      </c>
+      <c r="C74" s="49"/>
+      <c r="D74" s="49"/>
+    </row>
+    <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" s="49" t="s">
+        <v>164</v>
+      </c>
+      <c r="C75" s="49"/>
+      <c r="D75" s="49"/>
+    </row>
+    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" s="49" t="s">
+        <v>165</v>
+      </c>
+      <c r="C76" s="49"/>
+      <c r="D76" s="49"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" s="49" t="s">
+        <v>166</v>
+      </c>
+      <c r="C77" s="49"/>
+      <c r="D77" s="49"/>
+    </row>
+    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="42" t="n">
+        <v>6</v>
+      </c>
+      <c r="B79" s="43" t="s">
+        <v>167</v>
+      </c>
+      <c r="C79" s="43"/>
+      <c r="D79" s="43"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="B80" s="44"/>
+      <c r="C80" s="44"/>
+      <c r="D80" s="44"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="C82" s="46"/>
+      <c r="D82" s="47" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="C83" s="46"/>
+      <c r="D83" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="C84" s="46"/>
+      <c r="D84" s="47" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="C85" s="46"/>
+      <c r="D85" s="47" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" s="46"/>
+      <c r="D86" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" s="49" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" s="49"/>
+      <c r="D88" s="49"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="C89" s="49"/>
+      <c r="D89" s="49"/>
+    </row>
+    <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" s="49" t="s">
+        <v>177</v>
+      </c>
+      <c r="C90" s="49"/>
+      <c r="D90" s="49"/>
+    </row>
+    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="42" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" s="43" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" s="43"/>
+      <c r="D92" s="43"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="44" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" s="44"/>
+      <c r="C93" s="44"/>
+      <c r="D93" s="44"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="C95" s="46"/>
+      <c r="D95" s="47" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C96" s="46"/>
+      <c r="D96" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" s="46"/>
+      <c r="D97" s="47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="C98" s="46"/>
+      <c r="D98" s="47" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="C100" s="49"/>
+      <c r="D100" s="49"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="C101" s="49"/>
+      <c r="D101" s="49"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="C102" s="49"/>
+      <c r="D102" s="49"/>
+    </row>
+    <row r="103" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" s="49" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="49"/>
+      <c r="D103" s="49"/>
+    </row>
+    <row r="105" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="42" t="n">
+        <v>8</v>
+      </c>
+      <c r="B105" s="43" t="s">
+        <v>190</v>
+      </c>
+      <c r="C105" s="43"/>
+      <c r="D105" s="43"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="B106" s="44"/>
+      <c r="C106" s="44"/>
+      <c r="D106" s="44"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="46" t="s">
+        <v>192</v>
+      </c>
+      <c r="C108" s="46"/>
+      <c r="D108" s="47" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="46" t="s">
+        <v>193</v>
+      </c>
+      <c r="C109" s="46"/>
+      <c r="D109" s="47" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="46" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="46"/>
+      <c r="D110" s="47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="46" t="s">
+        <v>196</v>
+      </c>
+      <c r="C111" s="46"/>
+      <c r="D111" s="47" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="46" t="s">
+        <v>198</v>
+      </c>
+      <c r="C112" s="46"/>
+      <c r="D112" s="47" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B114" s="49" t="s">
+        <v>199</v>
+      </c>
+      <c r="C114" s="49"/>
+      <c r="D114" s="49"/>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B115" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="C115" s="49"/>
+      <c r="D115" s="49"/>
+    </row>
+    <row r="116" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B116" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="C116" s="49"/>
+      <c r="D116" s="49"/>
+    </row>
+    <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B117" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="C117" s="49"/>
+      <c r="D117" s="49"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B118" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="C118" s="49"/>
+      <c r="D118" s="49"/>
+    </row>
+    <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="42" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="C120" s="43"/>
+      <c r="D120" s="43"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="B121" s="44"/>
+      <c r="C121" s="44"/>
+      <c r="D121" s="44"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="46" t="s">
+        <v>132</v>
+      </c>
+      <c r="C123" s="46"/>
+      <c r="D123" s="47" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="46" t="s">
+        <v>207</v>
+      </c>
+      <c r="C124" s="46"/>
+      <c r="D124" s="47" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="46" t="s">
+        <v>208</v>
+      </c>
+      <c r="C125" s="46"/>
+      <c r="D125" s="47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="46" t="s">
+        <v>209</v>
+      </c>
+      <c r="C126" s="46"/>
+      <c r="D126" s="47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B127" s="46" t="s">
+        <v>210</v>
+      </c>
+      <c r="C127" s="46"/>
+      <c r="D127" s="47" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="C129" s="49"/>
+      <c r="D129" s="49"/>
+    </row>
+    <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="C130" s="49"/>
+      <c r="D130" s="49"/>
+    </row>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="C131" s="49"/>
+      <c r="D131" s="49"/>
+    </row>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="C132" s="49"/>
+      <c r="D132" s="49"/>
+    </row>
+    <row r="134" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C134" s="43"/>
+      <c r="D134" s="43"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="B135" s="44"/>
+      <c r="C135" s="44"/>
+      <c r="D135" s="44"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="45" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B137" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="C137" s="46"/>
+      <c r="D137" s="47" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="46" t="s">
+        <v>220</v>
+      </c>
+      <c r="C138" s="46"/>
+      <c r="D138" s="47" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B139" s="46" t="s">
+        <v>221</v>
+      </c>
+      <c r="C139" s="46"/>
+      <c r="D139" s="47" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="C140" s="46"/>
+      <c r="D140" s="47" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" s="49" t="s">
+        <v>224</v>
+      </c>
+      <c r="C142" s="49"/>
+      <c r="D142" s="49"/>
+    </row>
+    <row r="143" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" s="49" t="s">
+        <v>225</v>
+      </c>
+      <c r="C143" s="49"/>
+      <c r="D143" s="49"/>
+    </row>
+    <row r="144" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="49" t="s">
+        <v>226</v>
+      </c>
+      <c r="C144" s="49"/>
+      <c r="D144" s="49"/>
+    </row>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B145" s="49" t="s">
+        <v>227</v>
+      </c>
+      <c r="C145" s="49"/>
+      <c r="D145" s="49"/>
+    </row>
+  </sheetData>
+  <mergeCells count="114">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="B59:D59"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A65:D65"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B73:D73"/>
+    <mergeCell ref="B74:D74"/>
+    <mergeCell ref="B75:D75"/>
+    <mergeCell ref="B76:D76"/>
+    <mergeCell ref="B77:D77"/>
+    <mergeCell ref="B79:D79"/>
+    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="B89:D89"/>
+    <mergeCell ref="B90:D90"/>
+    <mergeCell ref="B92:D92"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="B95:C95"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B100:D100"/>
+    <mergeCell ref="B101:D101"/>
+    <mergeCell ref="B102:D102"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="B105:D105"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="B108:C108"/>
+    <mergeCell ref="B109:C109"/>
+    <mergeCell ref="B110:C110"/>
+    <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B114:D114"/>
+    <mergeCell ref="B115:D115"/>
+    <mergeCell ref="B116:D116"/>
+    <mergeCell ref="B117:D117"/>
+    <mergeCell ref="B118:D118"/>
+    <mergeCell ref="B120:D120"/>
+    <mergeCell ref="A121:D121"/>
+    <mergeCell ref="B123:C123"/>
+    <mergeCell ref="B124:C124"/>
+    <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="B129:D129"/>
+    <mergeCell ref="B130:D130"/>
+    <mergeCell ref="B131:D131"/>
+    <mergeCell ref="B132:D132"/>
+    <mergeCell ref="B134:D134"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
+    <mergeCell ref="B142:D142"/>
+    <mergeCell ref="B143:D143"/>
+    <mergeCell ref="B144:D144"/>
+    <mergeCell ref="B145:D145"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
 </file>
--- a/tracker-en.xlsx
+++ b/tracker-en.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="234">
   <si>
     <t xml:space="preserve">H</t>
   </si>
@@ -224,13 +224,31 @@
     <t xml:space="preserve">Note</t>
   </si>
   <si>
+    <t xml:space="preserve">BMI TOOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Height (cm)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">← enter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latest weight (kg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BMI = weight ÷ height². Rough measure (muscle not counted). Under 18.5 = underweight — don't lose more.</t>
+  </si>
+  <si>
     <t xml:space="preserve">SHOPPING LIST</t>
   </si>
   <si>
     <t xml:space="preserve">Your weekly list, by category. Tick what you already have.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Category</t>
   </si>
   <si>
     <t xml:space="preserve">Item</t>
@@ -714,7 +732,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0&quot; kg&quot;"/>
     <numFmt numFmtId="166" formatCode="\+0.0&quot; kg&quot;;\-0.0&quot; kg&quot;;0.0&quot; kg&quot;"/>
@@ -724,8 +742,9 @@
     <numFmt numFmtId="170" formatCode="0.0"/>
     <numFmt numFmtId="171" formatCode="mm\-dd\-yyyy"/>
     <numFmt numFmtId="172" formatCode="\+0.0;\-0.0"/>
+    <numFmt numFmtId="173" formatCode="General"/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="37">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -896,8 +915,69 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF8C8C8C"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FFE8321E"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -918,21 +998,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF8C8C8C"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FFE8321E"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
@@ -948,13 +1013,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="10"/>
       <color rgb="FF0A0A0A"/>
@@ -963,7 +1021,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1006,8 +1064,14 @@
         <bgColor rgb="FFFAFAFA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF4CC"/>
+        <bgColor rgb="FFFFF0ED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -1171,6 +1235,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1197,7 +1276,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1330,11 +1409,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="171" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1342,11 +1425,43 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="8" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="172" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="28" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="29" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="32" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1358,35 +1473,35 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="29" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="35" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1394,7 +1509,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1427,7 +1542,7 @@
       <rgbColor rgb="FF878787"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF0ED"/>
+      <rgbColor rgb="FFFFF4CC"/>
       <rgbColor rgb="FFF6F6F6"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF6A52"/>
@@ -1444,11 +1559,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFE6E6E6"/>
       <rgbColor rgb="FFFAFAFA"/>
-      <rgbColor rgb="FFFBFBFB"/>
+      <rgbColor rgb="FFFFF0ED"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFBFBFB"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -1463,7 +1578,7 @@
       <rgbColor rgb="FF444444"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF1F4E79"/>
       <rgbColor rgb="FF404040"/>
     </indexedColors>
   </colors>
@@ -1669,11 +1784,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="83911378"/>
-        <c:axId val="45546000"/>
+        <c:axId val="59863130"/>
+        <c:axId val="35206712"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="83911378"/>
+        <c:axId val="59863130"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1705,7 +1820,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45546000"/>
+        <c:crossAx val="35206712"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1713,7 +1828,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="45546000"/>
+        <c:axId val="35206712"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1745,7 +1860,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83911378"/>
+        <c:crossAx val="59863130"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1784,9 +1899,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>77760</xdr:colOff>
+      <xdr:colOff>77400</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>97560</xdr:rowOff>
+      <xdr:rowOff>97200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1795,7 +1910,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="1743120"/>
-        <a:ext cx="4139280" cy="1907280"/>
+        <a:ext cx="4138920" cy="1906920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3264,12 +3379,15 @@
     <tabColor rgb="FFD9D9D9"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3301,283 +3419,332 @@
       <c r="D3" s="28" t="s">
         <v>65</v>
       </c>
+      <c r="F3" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="33" t="n">
+      <c r="A4" s="34" t="n">
         <v>46271</v>
       </c>
-      <c r="B4" s="34" t="n">
+      <c r="B4" s="35" t="n">
         <v>88.6</v>
       </c>
       <c r="C4" s="30"/>
-      <c r="D4" s="35"/>
+      <c r="D4" s="36"/>
+      <c r="F4" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="G4" s="38"/>
+      <c r="H4" s="39" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="n">
+      <c r="A5" s="34" t="n">
         <v>46278</v>
       </c>
-      <c r="B5" s="34" t="n">
+      <c r="B5" s="35" t="n">
         <v>88.2</v>
       </c>
-      <c r="C5" s="36" t="n">
+      <c r="C5" s="40" t="n">
         <f aca="false">IF(AND(B5&lt;&gt;"",B4&lt;&gt;""),B5-B4,"")</f>
         <v>-0.399999999999992</v>
       </c>
-      <c r="D5" s="35"/>
+      <c r="D5" s="36"/>
+      <c r="F5" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="41" t="n">
+        <f aca="false">IFERROR(LOOKUP(2,1/(B4:B30&lt;&gt;""),B4:B30),"")</f>
+        <v>87</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="34" t="n">
         <v>46285</v>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="35" t="n">
         <v>88.4</v>
       </c>
-      <c r="C6" s="36" t="n">
+      <c r="C6" s="40" t="n">
         <f aca="false">IF(AND(B6&lt;&gt;"",B5&lt;&gt;""),B6-B5,"")</f>
         <v>0.200000000000003</v>
       </c>
-      <c r="D6" s="35"/>
+      <c r="D6" s="36"/>
+      <c r="F6" s="42" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="43" t="str">
+        <f aca="false">IF(AND(G4&gt;0,G5&gt;0),ROUND(G5/(G4/100)^2,1),"")</f>
+        <v/>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="34" t="n">
         <v>46292</v>
       </c>
-      <c r="B7" s="34" t="n">
+      <c r="B7" s="35" t="n">
         <v>87.9</v>
       </c>
-      <c r="C7" s="36" t="n">
+      <c r="C7" s="40" t="n">
         <f aca="false">IF(AND(B7&lt;&gt;"",B6&lt;&gt;""),B7-B6,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D7" s="35"/>
+      <c r="D7" s="36"/>
+      <c r="F7" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="44" t="str">
+        <f aca="false">IF(G6="","",IF(G6&lt;18.5,"Underweight",IF(G6&lt;25,"Healthy",IF(G6&lt;30,"Overweight","Obese"))))</f>
+        <v/>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="34" t="n">
         <v>46299</v>
       </c>
-      <c r="B8" s="34" t="n">
+      <c r="B8" s="35" t="n">
         <v>87.6</v>
       </c>
-      <c r="C8" s="36" t="n">
+      <c r="C8" s="40" t="n">
         <f aca="false">IF(AND(B8&lt;&gt;"",B7&lt;&gt;""),B8-B7,"")</f>
         <v>-0.300000000000011</v>
       </c>
-      <c r="D8" s="35"/>
+      <c r="D8" s="36"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="34" t="n">
         <v>46306</v>
       </c>
-      <c r="B9" s="34" t="n">
+      <c r="B9" s="35" t="n">
         <v>87.7</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="40" t="n">
         <f aca="false">IF(AND(B9&lt;&gt;"",B8&lt;&gt;""),B9-B8,"")</f>
         <v>0.100000000000009</v>
       </c>
-      <c r="D9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="F9" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="34" t="n">
         <v>46313</v>
       </c>
-      <c r="B10" s="34" t="n">
+      <c r="B10" s="35" t="n">
         <v>87.2</v>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="40" t="n">
         <f aca="false">IF(AND(B10&lt;&gt;"",B9&lt;&gt;""),B10-B9,"")</f>
         <v>-0.5</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="36"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="34" t="n">
         <v>46320</v>
       </c>
-      <c r="B11" s="34" t="n">
+      <c r="B11" s="35" t="n">
         <v>87</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="40" t="n">
         <f aca="false">IF(AND(B11&lt;&gt;"",B10&lt;&gt;""),B11-B10,"")</f>
         <v>-0.200000000000003</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="36"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="30"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="36" t="str">
+      <c r="B12" s="35"/>
+      <c r="C12" s="40" t="str">
         <f aca="false">IF(AND(B12&lt;&gt;"",B11&lt;&gt;""),B12-B11,"")</f>
         <v/>
       </c>
-      <c r="D12" s="35"/>
+      <c r="D12" s="36"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="30"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="36" t="str">
+      <c r="B13" s="35"/>
+      <c r="C13" s="40" t="str">
         <f aca="false">IF(AND(B13&lt;&gt;"",B12&lt;&gt;""),B13-B12,"")</f>
         <v/>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="36"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="30"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="36" t="str">
+      <c r="B14" s="35"/>
+      <c r="C14" s="40" t="str">
         <f aca="false">IF(AND(B14&lt;&gt;"",B13&lt;&gt;""),B14-B13,"")</f>
         <v/>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="36"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="30"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="36" t="str">
+      <c r="B15" s="35"/>
+      <c r="C15" s="40" t="str">
         <f aca="false">IF(AND(B15&lt;&gt;"",B14&lt;&gt;""),B15-B14,"")</f>
         <v/>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="36"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="30"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="36" t="str">
+      <c r="B16" s="35"/>
+      <c r="C16" s="40" t="str">
         <f aca="false">IF(AND(B16&lt;&gt;"",B15&lt;&gt;""),B16-B15,"")</f>
         <v/>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="36"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="30"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="36" t="str">
+      <c r="B17" s="35"/>
+      <c r="C17" s="40" t="str">
         <f aca="false">IF(AND(B17&lt;&gt;"",B16&lt;&gt;""),B17-B16,"")</f>
         <v/>
       </c>
-      <c r="D17" s="35"/>
+      <c r="D17" s="36"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="30"/>
-      <c r="B18" s="34"/>
-      <c r="C18" s="36" t="str">
+      <c r="B18" s="35"/>
+      <c r="C18" s="40" t="str">
         <f aca="false">IF(AND(B18&lt;&gt;"",B17&lt;&gt;""),B18-B17,"")</f>
         <v/>
       </c>
-      <c r="D18" s="35"/>
+      <c r="D18" s="36"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="30"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="36" t="str">
+      <c r="B19" s="35"/>
+      <c r="C19" s="40" t="str">
         <f aca="false">IF(AND(B19&lt;&gt;"",B18&lt;&gt;""),B19-B18,"")</f>
         <v/>
       </c>
-      <c r="D19" s="35"/>
+      <c r="D19" s="36"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="30"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="36" t="str">
+      <c r="B20" s="35"/>
+      <c r="C20" s="40" t="str">
         <f aca="false">IF(AND(B20&lt;&gt;"",B19&lt;&gt;""),B20-B19,"")</f>
         <v/>
       </c>
-      <c r="D20" s="35"/>
+      <c r="D20" s="36"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="30"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="36" t="str">
+      <c r="B21" s="35"/>
+      <c r="C21" s="40" t="str">
         <f aca="false">IF(AND(B21&lt;&gt;"",B20&lt;&gt;""),B21-B20,"")</f>
         <v/>
       </c>
-      <c r="D21" s="35"/>
+      <c r="D21" s="36"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="30"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="36" t="str">
+      <c r="B22" s="35"/>
+      <c r="C22" s="40" t="str">
         <f aca="false">IF(AND(B22&lt;&gt;"",B21&lt;&gt;""),B22-B21,"")</f>
         <v/>
       </c>
-      <c r="D22" s="35"/>
+      <c r="D22" s="36"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="30"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="36" t="str">
+      <c r="B23" s="35"/>
+      <c r="C23" s="40" t="str">
         <f aca="false">IF(AND(B23&lt;&gt;"",B22&lt;&gt;""),B23-B22,"")</f>
         <v/>
       </c>
-      <c r="D23" s="35"/>
+      <c r="D23" s="36"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="30"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="36" t="str">
+      <c r="B24" s="35"/>
+      <c r="C24" s="40" t="str">
         <f aca="false">IF(AND(B24&lt;&gt;"",B23&lt;&gt;""),B24-B23,"")</f>
         <v/>
       </c>
-      <c r="D24" s="35"/>
+      <c r="D24" s="36"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="30"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="36" t="str">
+      <c r="B25" s="35"/>
+      <c r="C25" s="40" t="str">
         <f aca="false">IF(AND(B25&lt;&gt;"",B24&lt;&gt;""),B25-B24,"")</f>
         <v/>
       </c>
-      <c r="D25" s="35"/>
+      <c r="D25" s="36"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="30"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="36" t="str">
+      <c r="B26" s="35"/>
+      <c r="C26" s="40" t="str">
         <f aca="false">IF(AND(B26&lt;&gt;"",B25&lt;&gt;""),B26-B25,"")</f>
         <v/>
       </c>
-      <c r="D26" s="35"/>
+      <c r="D26" s="36"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="30"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="36" t="str">
+      <c r="B27" s="35"/>
+      <c r="C27" s="40" t="str">
         <f aca="false">IF(AND(B27&lt;&gt;"",B26&lt;&gt;""),B27-B26,"")</f>
         <v/>
       </c>
-      <c r="D27" s="35"/>
+      <c r="D27" s="36"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="30"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="36" t="str">
+      <c r="B28" s="35"/>
+      <c r="C28" s="40" t="str">
         <f aca="false">IF(AND(B28&lt;&gt;"",B27&lt;&gt;""),B28-B27,"")</f>
         <v/>
       </c>
-      <c r="D28" s="35"/>
+      <c r="D28" s="36"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="30"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="36" t="str">
+      <c r="B29" s="35"/>
+      <c r="C29" s="40" t="str">
         <f aca="false">IF(AND(B29&lt;&gt;"",B28&lt;&gt;""),B29-B28,"")</f>
         <v/>
       </c>
-      <c r="D29" s="35"/>
+      <c r="D29" s="36"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="30"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="36" t="str">
+      <c r="B30" s="35"/>
+      <c r="C30" s="40" t="str">
         <f aca="false">IF(AND(B30&lt;&gt;"",B29&lt;&gt;""),B30-B29,"")</f>
         <v/>
       </c>
-      <c r="D30" s="35"/>
+      <c r="D30" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="F9:H12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3606,7 +3773,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -3614,7 +3781,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="27" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -3622,147 +3789,147 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C3" s="28" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D3" s="28" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="37" t="s">
-        <v>72</v>
+      <c r="A4" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="38"/>
-      <c r="D4" s="39"/>
+        <v>79</v>
+      </c>
+      <c r="C4" s="47"/>
+      <c r="D4" s="48"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="37" t="s">
-        <v>72</v>
+      <c r="A5" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
+        <v>80</v>
+      </c>
+      <c r="C5" s="47"/>
+      <c r="D5" s="48"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="37" t="s">
-        <v>72</v>
+      <c r="A6" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="38"/>
-      <c r="D6" s="39"/>
+        <v>81</v>
+      </c>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="37" t="s">
-        <v>72</v>
+      <c r="A7" s="46" t="s">
+        <v>78</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="39"/>
+        <v>82</v>
+      </c>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="38"/>
-      <c r="D8" s="39"/>
+        <v>83</v>
+      </c>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="39"/>
+        <v>84</v>
+      </c>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="37" t="s">
+      <c r="A10" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="29" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="39"/>
+        <v>85</v>
+      </c>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="37" t="s">
-        <v>80</v>
+      <c r="A11" s="46" t="s">
+        <v>86</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39"/>
+        <v>87</v>
+      </c>
+      <c r="C11" s="47"/>
+      <c r="D11" s="48"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="37" t="s">
-        <v>80</v>
+      <c r="A12" s="46" t="s">
+        <v>86</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="38"/>
-      <c r="D12" s="39"/>
+        <v>88</v>
+      </c>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="37" t="s">
-        <v>80</v>
+      <c r="A13" s="46" t="s">
+        <v>86</v>
       </c>
       <c r="B13" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39"/>
+        <v>89</v>
+      </c>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="37" t="s">
-        <v>84</v>
+      <c r="A14" s="46" t="s">
+        <v>90</v>
       </c>
       <c r="B14" s="29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C14" s="38"/>
-      <c r="D14" s="39"/>
+        <v>91</v>
+      </c>
+      <c r="C14" s="47"/>
+      <c r="D14" s="48"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="37" t="s">
-        <v>84</v>
+      <c r="A15" s="46" t="s">
+        <v>90</v>
       </c>
       <c r="B15" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39"/>
+        <v>92</v>
+      </c>
+      <c r="C15" s="47"/>
+      <c r="D15" s="48"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="37" t="s">
-        <v>84</v>
+      <c r="A16" s="46" t="s">
+        <v>90</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="38"/>
-      <c r="D16" s="39"/>
+        <v>93</v>
+      </c>
+      <c r="C16" s="47"/>
+      <c r="D16" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3787,1185 +3954,1185 @@
   <dimension ref="A1:D145"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="12"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="40" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="50" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="42" t="n">
+      <c r="A4" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="43" t="s">
-        <v>90</v>
-      </c>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="46"/>
-      <c r="D7" s="47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47" t="s">
+      <c r="B4" s="52" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="46" t="s">
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="53" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="46"/>
-      <c r="D9" s="47" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="54" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="46" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="55" t="s">
         <v>99</v>
       </c>
-      <c r="C10" s="46"/>
-      <c r="D10" s="47" t="s">
+      <c r="C7" s="55"/>
+      <c r="D7" s="56" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="46" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="47" t="s">
+      <c r="C8" s="55"/>
+      <c r="D8" s="56" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="45" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="55" t="s">
         <v>103</v>
       </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C10" s="55"/>
+      <c r="D10" s="56" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="C11" s="55"/>
+      <c r="D11" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="54" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="48" t="n">
+      <c r="A13" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+    </row>
+    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>111</v>
+      </c>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+    </row>
+    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+    </row>
+    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B16" s="58" t="s">
+        <v>113</v>
+      </c>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+    </row>
+    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+    </row>
+    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="53" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="55"/>
+      <c r="D22" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="49"/>
-    </row>
-    <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="48" t="n">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="55" t="s">
+        <v>118</v>
+      </c>
+      <c r="C23" s="55"/>
+      <c r="D23" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="C25" s="55"/>
+      <c r="D25" s="56" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="55"/>
+      <c r="D26" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="55"/>
+      <c r="D27" s="56" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+    </row>
+    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-    </row>
-    <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="48" t="n">
+      <c r="B30" s="58" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+    </row>
+    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="57" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="49" t="s">
+      <c r="B31" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+    </row>
+    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B32" s="58" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+    </row>
+    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B33" s="58" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+    </row>
+    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="52"/>
+      <c r="D35" s="52"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="B36" s="53"/>
+      <c r="C36" s="53"/>
+      <c r="D36" s="53"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="55" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C41" s="55"/>
+      <c r="D41" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="55"/>
+      <c r="D42" s="56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B44" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+    </row>
+    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B45" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+    </row>
+    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B46" s="58" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+    </row>
+    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B47" s="58" t="s">
+        <v>144</v>
+      </c>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+    </row>
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="B50" s="53"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="55"/>
+      <c r="D52" s="56" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="55" t="s">
+        <v>149</v>
+      </c>
+      <c r="C53" s="55"/>
+      <c r="D53" s="56" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="C54" s="55"/>
+      <c r="D54" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="55" t="s">
+        <v>152</v>
+      </c>
+      <c r="C55" s="55"/>
+      <c r="D55" s="56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="55" t="s">
+        <v>153</v>
+      </c>
+      <c r="C56" s="55"/>
+      <c r="D56" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B58" s="58" t="s">
+        <v>154</v>
+      </c>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+    </row>
+    <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B59" s="58" t="s">
+        <v>155</v>
+      </c>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+    </row>
+    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B60" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+    </row>
+    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B61" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B62" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+    </row>
+    <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>159</v>
+      </c>
+      <c r="C64" s="52"/>
+      <c r="D64" s="52"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="53" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" s="53"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="55" t="s">
+        <v>161</v>
+      </c>
+      <c r="C67" s="55"/>
+      <c r="D67" s="56" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="55" t="s">
+        <v>163</v>
+      </c>
+      <c r="C68" s="55"/>
+      <c r="D68" s="56" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="55" t="s">
+        <v>164</v>
+      </c>
+      <c r="C69" s="55"/>
+      <c r="D69" s="56" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="55" t="s">
+        <v>166</v>
+      </c>
+      <c r="C70" s="55"/>
+      <c r="D70" s="56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="55" t="s">
+        <v>167</v>
+      </c>
+      <c r="C71" s="55"/>
+      <c r="D71" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" s="58" t="s">
+        <v>168</v>
+      </c>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+    </row>
+    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A74" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B74" s="58" t="s">
+        <v>169</v>
+      </c>
+      <c r="C74" s="58"/>
+      <c r="D74" s="58"/>
+    </row>
+    <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B75" s="58" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" s="58"/>
+      <c r="D75" s="58"/>
+    </row>
+    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B76" s="58" t="s">
+        <v>171</v>
+      </c>
+      <c r="C76" s="58"/>
+      <c r="D76" s="58"/>
+    </row>
+    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B77" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+    </row>
+    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="B79" s="52" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="52"/>
+      <c r="D79" s="52"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A80" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="B80" s="53"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="55" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="55"/>
+      <c r="D82" s="56" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="55" t="s">
+        <v>176</v>
+      </c>
+      <c r="C83" s="55"/>
+      <c r="D83" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C84" s="55"/>
+      <c r="D84" s="56" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C85" s="55"/>
+      <c r="D85" s="56" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B86" s="55" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="55"/>
+      <c r="D86" s="56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A88" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B88" s="58" t="s">
+        <v>181</v>
+      </c>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
+    </row>
+    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A89" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B89" s="58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+    </row>
+    <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A90" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B90" s="58" t="s">
+        <v>183</v>
+      </c>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
+    </row>
+    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A92" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="B92" s="52" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" s="52"/>
+      <c r="D92" s="52"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A93" s="53" t="s">
+        <v>185</v>
+      </c>
+      <c r="B93" s="53"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="53"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A94" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B95" s="55" t="s">
+        <v>186</v>
+      </c>
+      <c r="C95" s="55"/>
+      <c r="D95" s="56" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B96" s="55" t="s">
+        <v>188</v>
+      </c>
+      <c r="C96" s="55"/>
+      <c r="D96" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B97" s="55" t="s">
+        <v>189</v>
+      </c>
+      <c r="C97" s="55"/>
+      <c r="D97" s="56" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B98" s="55" t="s">
+        <v>190</v>
+      </c>
+      <c r="C98" s="55"/>
+      <c r="D98" s="56" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A99" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A100" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B100" s="58" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="58"/>
+      <c r="D100" s="58"/>
+    </row>
+    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A101" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B101" s="58" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" s="58"/>
+      <c r="D101" s="58"/>
+    </row>
+    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A102" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B102" s="58" t="s">
+        <v>194</v>
+      </c>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+    </row>
+    <row r="103" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B103" s="58" t="s">
+        <v>195</v>
+      </c>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
+    </row>
+    <row r="105" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A105" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="B105" s="52" t="s">
+        <v>196</v>
+      </c>
+      <c r="C105" s="52"/>
+      <c r="D105" s="52"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A106" s="53" t="s">
+        <v>197</v>
+      </c>
+      <c r="B106" s="53"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="53"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A107" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B108" s="55" t="s">
+        <v>198</v>
+      </c>
+      <c r="C108" s="55"/>
+      <c r="D108" s="56" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B109" s="55" t="s">
+        <v>199</v>
+      </c>
+      <c r="C109" s="55"/>
+      <c r="D109" s="56" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B110" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="C110" s="55"/>
+      <c r="D110" s="56" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="55" t="s">
+        <v>202</v>
+      </c>
+      <c r="C111" s="55"/>
+      <c r="D111" s="56" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B112" s="55" t="s">
+        <v>204</v>
+      </c>
+      <c r="C112" s="55"/>
+      <c r="D112" s="56" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A113" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A114" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B114" s="58" t="s">
+        <v>205</v>
+      </c>
+      <c r="C114" s="58"/>
+      <c r="D114" s="58"/>
+    </row>
+    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A115" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B115" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C115" s="58"/>
+      <c r="D115" s="58"/>
+    </row>
+    <row r="116" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A116" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B116" s="58" t="s">
+        <v>207</v>
+      </c>
+      <c r="C116" s="58"/>
+      <c r="D116" s="58"/>
+    </row>
+    <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A117" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B117" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C117" s="58"/>
+      <c r="D117" s="58"/>
+    </row>
+    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A118" s="57" t="n">
+        <v>5</v>
+      </c>
+      <c r="B118" s="58" t="s">
+        <v>209</v>
+      </c>
+      <c r="C118" s="58"/>
+      <c r="D118" s="58"/>
+    </row>
+    <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A120" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="B120" s="52" t="s">
+        <v>210</v>
+      </c>
+      <c r="C120" s="52"/>
+      <c r="D120" s="52"/>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A121" s="53" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" s="53"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A122" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B123" s="55" t="s">
+        <v>138</v>
+      </c>
+      <c r="C123" s="55"/>
+      <c r="D123" s="56" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B124" s="55" t="s">
+        <v>213</v>
+      </c>
+      <c r="C124" s="55"/>
+      <c r="D124" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B125" s="55" t="s">
+        <v>214</v>
+      </c>
+      <c r="C125" s="55"/>
+      <c r="D125" s="56" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B126" s="55" t="s">
+        <v>215</v>
+      </c>
+      <c r="C126" s="55"/>
+      <c r="D126" s="56" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B127" s="55" t="s">
+        <v>216</v>
+      </c>
+      <c r="C127" s="55"/>
+      <c r="D127" s="56" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A128" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A129" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B129" s="58" t="s">
+        <v>218</v>
+      </c>
+      <c r="C129" s="58"/>
+      <c r="D129" s="58"/>
+    </row>
+    <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A130" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B130" s="58" t="s">
+        <v>219</v>
+      </c>
+      <c r="C130" s="58"/>
+      <c r="D130" s="58"/>
+    </row>
+    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A131" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B131" s="58" t="s">
+        <v>220</v>
+      </c>
+      <c r="C131" s="58"/>
+      <c r="D131" s="58"/>
+    </row>
+    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A132" s="57" t="n">
+        <v>4</v>
+      </c>
+      <c r="B132" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C132" s="58"/>
+      <c r="D132" s="58"/>
+    </row>
+    <row r="134" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A134" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="B134" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="C134" s="52"/>
+      <c r="D134" s="52"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A135" s="53" t="s">
+        <v>223</v>
+      </c>
+      <c r="B135" s="53"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="53"/>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A136" s="54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B137" s="55" t="s">
+        <v>224</v>
+      </c>
+      <c r="C137" s="55"/>
+      <c r="D137" s="56" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B138" s="55" t="s">
+        <v>226</v>
+      </c>
+      <c r="C138" s="55"/>
+      <c r="D138" s="56" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B139" s="55" t="s">
+        <v>227</v>
+      </c>
+      <c r="C139" s="55"/>
+      <c r="D139" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="49"/>
-    </row>
-    <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="48" t="n">
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B140" s="55" t="s">
+        <v>228</v>
+      </c>
+      <c r="C140" s="55"/>
+      <c r="D140" s="56" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A141" s="54" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A142" s="57" t="n">
+        <v>1</v>
+      </c>
+      <c r="B142" s="58" t="s">
+        <v>230</v>
+      </c>
+      <c r="C142" s="58"/>
+      <c r="D142" s="58"/>
+    </row>
+    <row r="143" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A143" s="57" t="n">
+        <v>2</v>
+      </c>
+      <c r="B143" s="58" t="s">
+        <v>231</v>
+      </c>
+      <c r="C143" s="58"/>
+      <c r="D143" s="58"/>
+    </row>
+    <row r="144" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A144" s="57" t="n">
+        <v>3</v>
+      </c>
+      <c r="B144" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C144" s="58"/>
+      <c r="D144" s="58"/>
+    </row>
+    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A145" s="57" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="49" t="s">
-        <v>107</v>
-      </c>
-      <c r="C16" s="49"/>
-      <c r="D16" s="49"/>
-    </row>
-    <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B17" s="49" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="49"/>
-    </row>
-    <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="42" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" s="43" t="s">
-        <v>109</v>
-      </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="C22" s="46"/>
-      <c r="D22" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="46"/>
-      <c r="D23" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24" s="46"/>
-      <c r="D24" s="47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="C25" s="46"/>
-      <c r="D25" s="47" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="46" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" s="46"/>
-      <c r="D26" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="46" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27" s="46"/>
-      <c r="D27" s="47" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B29" s="49" t="s">
-        <v>121</v>
-      </c>
-      <c r="C29" s="49"/>
-      <c r="D29" s="49"/>
-    </row>
-    <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B30" s="49" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" s="49"/>
-      <c r="D30" s="49"/>
-    </row>
-    <row r="31" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B31" s="49" t="s">
-        <v>123</v>
-      </c>
-      <c r="C31" s="49"/>
-      <c r="D31" s="49"/>
-    </row>
-    <row r="32" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B32" s="49" t="s">
-        <v>124</v>
-      </c>
-      <c r="C32" s="49"/>
-      <c r="D32" s="49"/>
-    </row>
-    <row r="33" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B33" s="49" t="s">
-        <v>125</v>
-      </c>
-      <c r="C33" s="49"/>
-      <c r="D33" s="49"/>
-    </row>
-    <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="42" t="n">
-        <v>3</v>
-      </c>
-      <c r="B35" s="43" t="s">
-        <v>126</v>
-      </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="44" t="s">
-        <v>127</v>
-      </c>
-      <c r="B36" s="44"/>
-      <c r="C36" s="44"/>
-      <c r="D36" s="44"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="46"/>
-      <c r="D38" s="47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C39" s="46"/>
-      <c r="D39" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="C40" s="46"/>
-      <c r="D40" s="47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="C41" s="46"/>
-      <c r="D41" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B44" s="49" t="s">
-        <v>135</v>
-      </c>
-      <c r="C44" s="49"/>
-      <c r="D44" s="49"/>
-    </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B45" s="49" t="s">
-        <v>136</v>
-      </c>
-      <c r="C45" s="49"/>
-      <c r="D45" s="49"/>
-    </row>
-    <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B46" s="49" t="s">
-        <v>137</v>
-      </c>
-      <c r="C46" s="49"/>
-      <c r="D46" s="49"/>
-    </row>
-    <row r="47" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B47" s="49" t="s">
-        <v>138</v>
-      </c>
-      <c r="C47" s="49"/>
-      <c r="D47" s="49"/>
-    </row>
-    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="42" t="n">
-        <v>4</v>
-      </c>
-      <c r="B49" s="43" t="s">
-        <v>139</v>
-      </c>
-      <c r="C49" s="43"/>
-      <c r="D49" s="43"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
-      <c r="D50" s="44"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="C52" s="46"/>
-      <c r="D52" s="47" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="46" t="s">
-        <v>143</v>
-      </c>
-      <c r="C53" s="46"/>
-      <c r="D53" s="47" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="C54" s="46"/>
-      <c r="D54" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="C55" s="46"/>
-      <c r="D55" s="47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="46" t="s">
-        <v>147</v>
-      </c>
-      <c r="C56" s="46"/>
-      <c r="D56" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B58" s="49" t="s">
-        <v>148</v>
-      </c>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-    </row>
-    <row r="59" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B59" s="49" t="s">
-        <v>149</v>
-      </c>
-      <c r="C59" s="49"/>
-      <c r="D59" s="49"/>
-    </row>
-    <row r="60" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B60" s="49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-    </row>
-    <row r="61" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B61" s="49" t="s">
-        <v>151</v>
-      </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-    </row>
-    <row r="62" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B62" s="49" t="s">
-        <v>152</v>
-      </c>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-    </row>
-    <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="42" t="n">
-        <v>5</v>
-      </c>
-      <c r="B64" s="43" t="s">
-        <v>153</v>
-      </c>
-      <c r="C64" s="43"/>
-      <c r="D64" s="43"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="B65" s="44"/>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="46" t="s">
-        <v>155</v>
-      </c>
-      <c r="C67" s="46"/>
-      <c r="D67" s="47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="C68" s="46"/>
-      <c r="D68" s="47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="46" t="s">
-        <v>158</v>
-      </c>
-      <c r="C69" s="46"/>
-      <c r="D69" s="47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="46" t="s">
-        <v>160</v>
-      </c>
-      <c r="C70" s="46"/>
-      <c r="D70" s="47" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="46" t="s">
-        <v>161</v>
-      </c>
-      <c r="C71" s="46"/>
-      <c r="D71" s="47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="49" t="s">
-        <v>162</v>
-      </c>
-      <c r="C73" s="49"/>
-      <c r="D73" s="49"/>
-    </row>
-    <row r="74" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B74" s="49" t="s">
-        <v>163</v>
-      </c>
-      <c r="C74" s="49"/>
-      <c r="D74" s="49"/>
-    </row>
-    <row r="75" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" s="49" t="s">
-        <v>164</v>
-      </c>
-      <c r="C75" s="49"/>
-      <c r="D75" s="49"/>
-    </row>
-    <row r="76" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B76" s="49" t="s">
-        <v>165</v>
-      </c>
-      <c r="C76" s="49"/>
-      <c r="D76" s="49"/>
-    </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="49" t="s">
-        <v>166</v>
-      </c>
-      <c r="C77" s="49"/>
-      <c r="D77" s="49"/>
-    </row>
-    <row r="79" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="42" t="n">
-        <v>6</v>
-      </c>
-      <c r="B79" s="43" t="s">
-        <v>167</v>
-      </c>
-      <c r="C79" s="43"/>
-      <c r="D79" s="43"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="B80" s="44"/>
-      <c r="C80" s="44"/>
-      <c r="D80" s="44"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="46" t="s">
-        <v>169</v>
-      </c>
-      <c r="C82" s="46"/>
-      <c r="D82" s="47" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="C83" s="46"/>
-      <c r="D83" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="C84" s="46"/>
-      <c r="D84" s="47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="46" t="s">
-        <v>172</v>
-      </c>
-      <c r="C85" s="46"/>
-      <c r="D85" s="47" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="C86" s="46"/>
-      <c r="D86" s="47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B88" s="49" t="s">
-        <v>175</v>
-      </c>
-      <c r="C88" s="49"/>
-      <c r="D88" s="49"/>
-    </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B89" s="49" t="s">
-        <v>176</v>
-      </c>
-      <c r="C89" s="49"/>
-      <c r="D89" s="49"/>
-    </row>
-    <row r="90" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B90" s="49" t="s">
-        <v>177</v>
-      </c>
-      <c r="C90" s="49"/>
-      <c r="D90" s="49"/>
-    </row>
-    <row r="92" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="42" t="n">
-        <v>7</v>
-      </c>
-      <c r="B92" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="C92" s="43"/>
-      <c r="D92" s="43"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="B93" s="44"/>
-      <c r="C93" s="44"/>
-      <c r="D93" s="44"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="C95" s="46"/>
-      <c r="D95" s="47" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="C96" s="46"/>
-      <c r="D96" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="46" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" s="46"/>
-      <c r="D97" s="47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="C98" s="46"/>
-      <c r="D98" s="47" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B100" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="C100" s="49"/>
-      <c r="D100" s="49"/>
-    </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B101" s="49" t="s">
-        <v>187</v>
-      </c>
-      <c r="C101" s="49"/>
-      <c r="D101" s="49"/>
-    </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B102" s="49" t="s">
-        <v>188</v>
-      </c>
-      <c r="C102" s="49"/>
-      <c r="D102" s="49"/>
-    </row>
-    <row r="103" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B103" s="49" t="s">
-        <v>189</v>
-      </c>
-      <c r="C103" s="49"/>
-      <c r="D103" s="49"/>
-    </row>
-    <row r="105" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="42" t="n">
-        <v>8</v>
-      </c>
-      <c r="B105" s="43" t="s">
-        <v>190</v>
-      </c>
-      <c r="C105" s="43"/>
-      <c r="D105" s="43"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="B106" s="44"/>
-      <c r="C106" s="44"/>
-      <c r="D106" s="44"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="C108" s="46"/>
-      <c r="D108" s="47" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="C109" s="46"/>
-      <c r="D109" s="47" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="46" t="s">
-        <v>195</v>
-      </c>
-      <c r="C110" s="46"/>
-      <c r="D110" s="47" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="C111" s="46"/>
-      <c r="D111" s="47" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="46" t="s">
-        <v>198</v>
-      </c>
-      <c r="C112" s="46"/>
-      <c r="D112" s="47" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B114" s="49" t="s">
-        <v>199</v>
-      </c>
-      <c r="C114" s="49"/>
-      <c r="D114" s="49"/>
-    </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B115" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="C115" s="49"/>
-      <c r="D115" s="49"/>
-    </row>
-    <row r="116" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B116" s="49" t="s">
-        <v>201</v>
-      </c>
-      <c r="C116" s="49"/>
-      <c r="D116" s="49"/>
-    </row>
-    <row r="117" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B117" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="C117" s="49"/>
-      <c r="D117" s="49"/>
-    </row>
-    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="B118" s="49" t="s">
-        <v>203</v>
-      </c>
-      <c r="C118" s="49"/>
-      <c r="D118" s="49"/>
-    </row>
-    <row r="120" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="42" t="n">
-        <v>9</v>
-      </c>
-      <c r="B120" s="43" t="s">
-        <v>204</v>
-      </c>
-      <c r="C120" s="43"/>
-      <c r="D120" s="43"/>
-    </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="44" t="s">
-        <v>205</v>
-      </c>
-      <c r="B121" s="44"/>
-      <c r="C121" s="44"/>
-      <c r="D121" s="44"/>
-    </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B123" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="C123" s="46"/>
-      <c r="D123" s="47" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B124" s="46" t="s">
-        <v>207</v>
-      </c>
-      <c r="C124" s="46"/>
-      <c r="D124" s="47" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B125" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="C125" s="46"/>
-      <c r="D125" s="47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="46" t="s">
-        <v>209</v>
-      </c>
-      <c r="C126" s="46"/>
-      <c r="D126" s="47" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B127" s="46" t="s">
-        <v>210</v>
-      </c>
-      <c r="C127" s="46"/>
-      <c r="D127" s="47" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B129" s="49" t="s">
-        <v>212</v>
-      </c>
-      <c r="C129" s="49"/>
-      <c r="D129" s="49"/>
-    </row>
-    <row r="130" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B130" s="49" t="s">
-        <v>213</v>
-      </c>
-      <c r="C130" s="49"/>
-      <c r="D130" s="49"/>
-    </row>
-    <row r="131" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B131" s="49" t="s">
-        <v>214</v>
-      </c>
-      <c r="C131" s="49"/>
-      <c r="D131" s="49"/>
-    </row>
-    <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B132" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="C132" s="49"/>
-      <c r="D132" s="49"/>
-    </row>
-    <row r="134" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="42" t="n">
-        <v>10</v>
-      </c>
-      <c r="B134" s="43" t="s">
-        <v>216</v>
-      </c>
-      <c r="C134" s="43"/>
-      <c r="D134" s="43"/>
-    </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="44" t="s">
-        <v>217</v>
-      </c>
-      <c r="B135" s="44"/>
-      <c r="C135" s="44"/>
-      <c r="D135" s="44"/>
-    </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B137" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="C137" s="46"/>
-      <c r="D137" s="47" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B138" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="C138" s="46"/>
-      <c r="D138" s="47" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B139" s="46" t="s">
-        <v>221</v>
-      </c>
-      <c r="C139" s="46"/>
-      <c r="D139" s="47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B140" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="C140" s="46"/>
-      <c r="D140" s="47" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="45" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="48" t="n">
-        <v>1</v>
-      </c>
-      <c r="B142" s="49" t="s">
-        <v>224</v>
-      </c>
-      <c r="C142" s="49"/>
-      <c r="D142" s="49"/>
-    </row>
-    <row r="143" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="48" t="n">
-        <v>2</v>
-      </c>
-      <c r="B143" s="49" t="s">
-        <v>225</v>
-      </c>
-      <c r="C143" s="49"/>
-      <c r="D143" s="49"/>
-    </row>
-    <row r="144" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="48" t="n">
-        <v>3</v>
-      </c>
-      <c r="B144" s="49" t="s">
-        <v>226</v>
-      </c>
-      <c r="C144" s="49"/>
-      <c r="D144" s="49"/>
-    </row>
-    <row r="145" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="48" t="n">
-        <v>4</v>
-      </c>
-      <c r="B145" s="49" t="s">
-        <v>227</v>
-      </c>
-      <c r="C145" s="49"/>
-      <c r="D145" s="49"/>
+      <c r="B145" s="58" t="s">
+        <v>233</v>
+      </c>
+      <c r="C145" s="58"/>
+      <c r="D145" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="114">

--- a/tracker-en.xlsx
+++ b/tracker-en.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="F5" s="69" t="n"/>
       <c r="G5" s="71">
-        <f>IF(N3="","",IF(N3&lt;-0.01,"! Too fast",IF(N3&lt;-0.003,"✓ On track",IF(N3&lt;=0.003,"– Stable",IF(N3&lt;=0.01,"✓ On track","! Too fast")))))</f>
+        <f>IF(OR(N1="",N2=""),"",IF(N2/N1*1000&lt;-10,"⚠ Too fast",IF(N2/N1*1000&lt;-3,"✓ On track",IF(N2/N1*1000&lt;=3,"– Stable",IF(N2/N1*1000&lt;=10,"✓ On track","⚠ Too fast")))))</f>
         <v/>
       </c>
       <c r="I5" s="69" t="n"/>
@@ -3202,7 +3202,7 @@
         </is>
       </c>
       <c r="G5" s="110">
-        <f>IF(COUNT(B4:B30)&gt;=1,INDEX(B4:B30,COUNT(B4:B30)),"")</f>
+        <f>IF(COUNT(Weight!$B$4:$B$30)&gt;=1,INDEX(Weight!$B$4:$B$30,COUNT(Weight!$B$4:$B$30)),"")</f>
         <v/>
       </c>
     </row>
